--- a/docs/data/jp/xlsx/8035.xlsx
+++ b/docs/data/jp/xlsx/8035.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC164"/>
+  <dimension ref="A1:AC171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4381,10 +4384,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>9110</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4419,7 +4424,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>468032733</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5618,7 +5625,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5870,802 +5877,875 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>238099</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>241549</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>291177</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>291049</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>306615</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>342792</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>344824</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>295616</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>345191</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>316216</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>378629</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>389676</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>308875</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>306607</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>291177</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>344824</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>378629</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>189727</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>222113</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>256116</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>264022</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>259940</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>311747</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>310578</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>253970</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>284891</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>235831</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>333188</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>342712</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>255942</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>251690</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>256116</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>310578</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>333188</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>연구개발비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>51039</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>49790</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>58405</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>53436</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>62056</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>61806</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>72719</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>62141</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>72686</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>66242</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>76797</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>72046</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>44160</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>53769</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>58405</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>72719</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>76797</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C82" s="22" t="n">
-        <v>42544</v>
-      </c>
-      <c r="D82" s="22" t="n">
-        <v>39862</v>
-      </c>
-      <c r="E82" s="22" t="n">
-        <v>9101</v>
-      </c>
-      <c r="F82" s="22" t="n">
-        <v>44852</v>
-      </c>
-      <c r="G82" s="22" t="n">
-        <v>49712</v>
-      </c>
-      <c r="H82" s="22" t="n">
-        <v>50325</v>
-      </c>
-      <c r="I82" s="22" t="n">
-        <v>3092</v>
-      </c>
-      <c r="J82" s="22" t="n">
-        <v>47134</v>
-      </c>
-      <c r="K82" s="22" t="n">
-        <v>53746</v>
-      </c>
-      <c r="L82" s="22" t="n">
-        <v>53450</v>
-      </c>
-      <c r="M82" s="22" t="n">
-        <v>-5168</v>
-      </c>
-      <c r="N82" s="22" t="n">
-        <v>59257</v>
-      </c>
-      <c r="T82" s="22" t="n">
-        <v>43203</v>
-      </c>
-      <c r="U82" s="22" t="n">
-        <v>9054</v>
-      </c>
-      <c r="V82" s="22" t="n">
-        <v>9101</v>
-      </c>
-      <c r="W82" s="22" t="n">
-        <v>3092</v>
-      </c>
-      <c r="X82" s="22" t="n">
-        <v>-5168</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>판매비와 관리비 합계</t>
+          <t>연구개발비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>93582</v>
+        <v>51039</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>89653</v>
+        <v>49790</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>110891</v>
+        <v>58405</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>98288</v>
+        <v>53436</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>111769</v>
+        <v>62056</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>112131</v>
+        <v>61806</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>126779</v>
+        <v>72719</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>109275</v>
+        <v>62141</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>126432</v>
+        <v>72686</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>119692</v>
+        <v>66242</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>127545</v>
+        <v>76797</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>131304</v>
+        <v>72046</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>87363</v>
+        <v>44160</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>98903</v>
+        <v>53769</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>110891</v>
+        <v>58405</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>126779</v>
+        <v>72719</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>127545</v>
+        <v>76797</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="n">
-        <v>96145</v>
-      </c>
-      <c r="D84" s="12" t="n">
-        <v>132460</v>
-      </c>
-      <c r="E84" s="12" t="n">
-        <v>145225</v>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>165733</v>
-      </c>
-      <c r="G84" s="12" t="n">
-        <v>148171</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>199617</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>183798</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>144694</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>158459</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>116140</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>205643</v>
-      </c>
-      <c r="N84" s="12" t="n">
-        <v>211407</v>
-      </c>
-      <c r="T84" s="12" t="n">
-        <v>168580</v>
-      </c>
-      <c r="U84" s="12" t="n">
-        <v>152787</v>
-      </c>
-      <c r="V84" s="12" t="n">
-        <v>145225</v>
-      </c>
-      <c r="W84" s="12" t="n">
-        <v>183798</v>
-      </c>
-      <c r="X84" s="12" t="n">
-        <v>205643</v>
+      <c r="A84" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="n">
+        <v>42544</v>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>39862</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>9101</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>44852</v>
+      </c>
+      <c r="G84" s="22" t="n">
+        <v>49712</v>
+      </c>
+      <c r="H84" s="22" t="n">
+        <v>50325</v>
+      </c>
+      <c r="I84" s="22" t="n">
+        <v>3092</v>
+      </c>
+      <c r="J84" s="22" t="n">
+        <v>47134</v>
+      </c>
+      <c r="K84" s="22" t="n">
+        <v>53746</v>
+      </c>
+      <c r="L84" s="22" t="n">
+        <v>53450</v>
+      </c>
+      <c r="M84" s="22" t="n">
+        <v>-5168</v>
+      </c>
+      <c r="N84" s="22" t="n">
+        <v>59257</v>
+      </c>
+      <c r="T84" s="22" t="n">
+        <v>43203</v>
+      </c>
+      <c r="U84" s="22" t="n">
+        <v>9054</v>
+      </c>
+      <c r="V84" s="22" t="n">
+        <v>9101</v>
+      </c>
+      <c r="W84" s="22" t="n">
+        <v>3092</v>
+      </c>
+      <c r="X84" s="22" t="n">
+        <v>-5168</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>배당금수익</t>
-        </is>
+          <t>판매비와 관리비 합계</t>
+        </is>
+      </c>
+      <c r="C85" s="22" t="n">
+        <v>93582</v>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>89653</v>
+      </c>
+      <c r="E85" s="22" t="n">
+        <v>110891</v>
       </c>
       <c r="F85" s="22" t="n">
-        <v>1344</v>
+        <v>98288</v>
       </c>
       <c r="G85" s="22" t="n">
-        <v>0</v>
+        <v>111769</v>
+      </c>
+      <c r="H85" s="22" t="n">
+        <v>112131</v>
+      </c>
+      <c r="I85" s="22" t="n">
+        <v>126779</v>
       </c>
       <c r="J85" s="22" t="n">
-        <v>1429</v>
+        <v>109275</v>
       </c>
       <c r="K85" s="22" t="n">
-        <v>0</v>
+        <v>126432</v>
+      </c>
+      <c r="L85" s="22" t="n">
+        <v>119692</v>
+      </c>
+      <c r="M85" s="22" t="n">
+        <v>127545</v>
       </c>
       <c r="N85" s="22" t="n">
-        <v>1158</v>
+        <v>131304</v>
+      </c>
+      <c r="T85" s="22" t="n">
+        <v>87363</v>
+      </c>
+      <c r="U85" s="22" t="n">
+        <v>98903</v>
+      </c>
+      <c r="V85" s="22" t="n">
+        <v>110891</v>
+      </c>
+      <c r="W85" s="22" t="n">
+        <v>126779</v>
+      </c>
+      <c r="X85" s="22" t="n">
+        <v>127545</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>810</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>852</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>987</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>843</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>1116</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>951</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>417</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>973</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>987</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>1116</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>951</v>
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>96145</v>
+      </c>
+      <c r="D86" s="12" t="n">
+        <v>132460</v>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>145225</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>165733</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>148171</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>199617</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>183798</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>144694</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>158459</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>116140</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>205643</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>211407</v>
+      </c>
+      <c r="T86" s="12" t="n">
+        <v>168580</v>
+      </c>
+      <c r="U86" s="12" t="n">
+        <v>152787</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>145225</v>
+      </c>
+      <c r="W86" s="12" t="n">
+        <v>183798</v>
+      </c>
+      <c r="X86" s="12" t="n">
+        <v>205643</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="F87" s="22" t="n">
-        <v>315</v>
-      </c>
-      <c r="J87" s="22" t="n">
-        <v>1083</v>
-      </c>
-      <c r="N87" s="22" t="n">
-        <v>1952</v>
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C87" s="17">
+        <f>IF(OR(C86="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C86/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D87" s="17">
+        <f>IF(OR(D86="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D86/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E87" s="17">
+        <f>IF(OR(E86="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E86/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>IF(OR(F86="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F86/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G87" s="17">
+        <f>IF(OR(G86="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G86/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H87" s="17">
+        <f>IF(OR(H86="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H86/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I87" s="17">
+        <f>IF(OR(I86="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I86/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J87" s="17">
+        <f>IF(OR(J86="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J86/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>IF(OR(K86="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K86/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L87" s="17">
+        <f>IF(OR(L86="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L86/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M87" s="17">
+        <f>IF(OR(M86="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M86/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N87" s="17">
+        <f>IF(OR(N86="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N86/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T87" s="17">
+        <f>IF(OR(T86="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T86/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U87" s="17">
+        <f>IF(OR(U86="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U86/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V87" s="17">
+        <f>IF(OR(V86="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V86/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W87" s="17">
+        <f>IF(OR(W86="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W86/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X87" s="17">
+        <f>IF(OR(X86="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X86/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C88" s="22" t="n">
-        <v>4450</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>2759</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>-6040</v>
-      </c>
-      <c r="F88" s="22" t="n">
-        <v>2009</v>
-      </c>
-      <c r="G88" s="22" t="n">
-        <v>4616</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>1295</v>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>-4458</v>
-      </c>
-      <c r="J88" s="22" t="n">
-        <v>1919</v>
-      </c>
-      <c r="K88" s="22" t="n">
-        <v>3067</v>
-      </c>
-      <c r="L88" s="22" t="n">
-        <v>1816</v>
-      </c>
-      <c r="M88" s="22" t="n">
-        <v>-3608</v>
-      </c>
-      <c r="N88" s="22" t="n">
-        <v>1836</v>
-      </c>
-      <c r="T88" s="22" t="n">
-        <v>-1459</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>-1746</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>-6040</v>
-      </c>
-      <c r="W88" s="22" t="n">
-        <v>-4458</v>
-      </c>
-      <c r="X88" s="22" t="n">
-        <v>-3608</v>
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G88" s="17">
+        <f>IF(OR(G86="",C86=""),"",IF(C86&lt;=0,"",IFERROR(G86/C86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="17">
+        <f>IF(OR(H86="",D86=""),"",IF(D86&lt;=0,"",IFERROR(H86/D86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="17">
+        <f>IF(OR(I86="",E86=""),"",IF(E86&lt;=0,"",IFERROR(I86/E86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="17">
+        <f>IF(OR(J86="",F86=""),"",IF(F86&lt;=0,"",IFERROR(J86/F86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>IF(OR(K86="",G86=""),"",IF(G86&lt;=0,"",IFERROR(K86/G86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="17">
+        <f>IF(OR(L86="",H86=""),"",IF(H86&lt;=0,"",IFERROR(L86/H86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="17">
+        <f>IF(OR(M86="",I86=""),"",IF(I86&lt;=0,"",IFERROR(M86/I86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="17">
+        <f>IF(OR(N86="",J86=""),"",IF(J86&lt;=0,"",IFERROR(N86/J86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T88" s="17">
+        <f>IF(OR(T86="",S86=""),"",IF(S86&lt;=0,"",IFERROR(T86/S86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U88" s="17">
+        <f>IF(OR(U86="",T86=""),"",IF(T86&lt;=0,"",IFERROR(U86/T86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="17">
+        <f>IF(OR(V86="",U86=""),"",IF(U86&lt;=0,"",IFERROR(V86/U86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="17">
+        <f>IF(OR(W86="",V86=""),"",IF(V86&lt;=0,"",IFERROR(W86/V86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="17">
+        <f>IF(OR(X86="",W86=""),"",IF(W86&lt;=0,"",IFERROR(X86/W86-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="n">
-        <v>2585</v>
-      </c>
-      <c r="D89" s="22" t="n">
-        <v>2759</v>
-      </c>
-      <c r="E89" s="22" t="n">
-        <v>3516</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F89" s="22" t="n">
-        <v>3669</v>
+        <v>1344</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H89" s="22" t="n">
-        <v>1836</v>
-      </c>
-      <c r="I89" s="22" t="n">
-        <v>2822</v>
+        <v>0</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>4432</v>
+        <v>1429</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>1983</v>
-      </c>
-      <c r="L89" s="22" t="n">
-        <v>2127</v>
-      </c>
-      <c r="M89" s="22" t="n">
-        <v>2216</v>
+        <v>0</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>4947</v>
-      </c>
-      <c r="T89" s="22" t="n">
-        <v>1026</v>
-      </c>
-      <c r="U89" s="22" t="n">
-        <v>3021</v>
-      </c>
-      <c r="V89" s="22" t="n">
-        <v>3516</v>
-      </c>
-      <c r="W89" s="22" t="n">
-        <v>2822</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>2216</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>40</v>
+        <v>810</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>317</v>
+        <v>852</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>1337</v>
+        <v>987</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>1651</v>
-      </c>
-      <c r="G90" s="22" t="n">
-        <v>-1651</v>
-      </c>
-      <c r="H90" s="22" t="n">
-        <v>1060</v>
+        <v>843</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>-131</v>
-      </c>
-      <c r="J90" s="22" t="n">
-        <v>1683</v>
-      </c>
-      <c r="K90" s="22" t="n">
-        <v>716</v>
-      </c>
-      <c r="L90" s="22" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>1037</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>504</v>
+        <v>951</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>866</v>
+        <v>417</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>642</v>
+        <v>973</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>1337</v>
+        <v>987</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>-131</v>
+        <v>1116</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>1037</v>
+        <v>951</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
-        <v>360</v>
-      </c>
-      <c r="D91" s="22" t="n">
-        <v>313</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>184</v>
+          <t>보조금 수입</t>
+        </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>352</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>340</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>183</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>414</v>
+        <v>315</v>
       </c>
       <c r="J91" s="22" t="n">
-        <v>96</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>177</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>249</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>280</v>
+        <v>1083</v>
       </c>
       <c r="N91" s="22" t="n">
-        <v>224</v>
-      </c>
-      <c r="T91" s="22" t="n">
-        <v>396</v>
-      </c>
-      <c r="U91" s="22" t="n">
-        <v>209</v>
-      </c>
-      <c r="V91" s="22" t="n">
-        <v>184</v>
-      </c>
-      <c r="W91" s="22" t="n">
-        <v>414</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>280</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>494</v>
+        <v>4450</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>537</v>
+        <v>2759</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>1520</v>
+        <v>-6040</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>-1312</v>
+        <v>4616</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>1243</v>
+        <v>1295</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>284</v>
+        <v>-4458</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>1779</v>
+        <v>1919</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>893</v>
+        <v>3067</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>1367</v>
+        <v>1816</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>1317</v>
+        <v>-3608</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>728</v>
+        <v>1836</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>1262</v>
+        <v>-1459</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>851</v>
+        <v>-1746</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>1520</v>
+        <v>-6040</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>284</v>
+        <v>-4458</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>1317</v>
+        <v>-3608</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="n">
-        <v>98236</v>
-      </c>
-      <c r="D93" s="12" t="n">
-        <v>134682</v>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v>147221</v>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>167398</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>153783</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>200210</v>
-      </c>
-      <c r="I93" s="12" t="n">
-        <v>186336</v>
-      </c>
-      <c r="J93" s="12" t="n">
-        <v>147347</v>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>159549</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>116900</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>206542</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>215626</v>
-      </c>
-      <c r="T93" s="12" t="n">
-        <v>168344</v>
-      </c>
-      <c r="U93" s="12" t="n">
-        <v>154956</v>
-      </c>
-      <c r="V93" s="12" t="n">
-        <v>147221</v>
-      </c>
-      <c r="W93" s="12" t="n">
-        <v>186336</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>206542</v>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>2585</v>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>2759</v>
+      </c>
+      <c r="E93" s="22" t="n">
+        <v>3516</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>3669</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>4300</v>
+      </c>
+      <c r="H93" s="22" t="n">
+        <v>1836</v>
+      </c>
+      <c r="I93" s="22" t="n">
+        <v>2822</v>
+      </c>
+      <c r="J93" s="22" t="n">
+        <v>4432</v>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>1983</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>2127</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>2216</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>4947</v>
+      </c>
+      <c r="T93" s="22" t="n">
+        <v>1026</v>
+      </c>
+      <c r="U93" s="22" t="n">
+        <v>3021</v>
+      </c>
+      <c r="V93" s="22" t="n">
+        <v>3516</v>
+      </c>
+      <c r="W93" s="22" t="n">
+        <v>2822</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>2216</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
-        </is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>317</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>1651</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>-1651</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>0</v>
+        <v>1060</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>0</v>
+        <v>-131</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>1683</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>716</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>37216</v>
+        <v>1117</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>76610</v>
+        <v>1037</v>
+      </c>
+      <c r="N94" s="22" t="n">
+        <v>504</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>866</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>642</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>1337</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>0</v>
+        <v>-131</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>76610</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="95">
@@ -6674,733 +6754,694 @@
           <t>기타</t>
         </is>
       </c>
+      <c r="C95" s="22" t="n">
+        <v>360</v>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>313</v>
+      </c>
+      <c r="E95" s="22" t="n">
+        <v>184</v>
+      </c>
       <c r="F95" s="22" t="n">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>4</v>
+        <v>340</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>12</v>
+        <v>414</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="K95" s="22" t="n">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="L95" s="22" t="n">
-        <v>4868</v>
+        <v>249</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>316</v>
+        <v>280</v>
+      </c>
+      <c r="N95" s="22" t="n">
+        <v>224</v>
+      </c>
+      <c r="T95" s="22" t="n">
+        <v>396</v>
+      </c>
+      <c r="U95" s="22" t="n">
+        <v>209</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>184</v>
       </c>
       <c r="W95" s="22" t="n">
-        <v>12</v>
+        <v>414</v>
       </c>
       <c r="X95" s="22" t="n">
-        <v>316</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>9</v>
+        <v>494</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>10607</v>
+        <v>1520</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>14</v>
+        <v>2004</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>4</v>
+        <v>-1312</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>1</v>
+        <v>1243</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>12</v>
+        <v>284</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>24</v>
+        <v>1779</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>893</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>1317</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>15</v>
+        <v>728</v>
       </c>
       <c r="T96" s="22" t="n">
-        <v>66</v>
+        <v>1262</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>886</v>
+        <v>851</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>10607</v>
+        <v>1520</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>12</v>
+        <v>284</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>1317</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>Gain On Refund Of Value Added Tax EI</t>
-        </is>
-      </c>
-      <c r="F97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>4849</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="22" t="n">
-        <v>0</v>
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>98236</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>134682</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>147221</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>167398</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>153783</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>200210</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>186336</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>147347</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>159549</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>116900</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>206542</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>215626</v>
+      </c>
+      <c r="T97" s="12" t="n">
+        <v>168344</v>
+      </c>
+      <c r="U97" s="12" t="n">
+        <v>154956</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>147221</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>186336</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>206542</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>특별이익 합계</t>
-        </is>
-      </c>
-      <c r="C98" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="D98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>10828</v>
-      </c>
-      <c r="F98" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="G98" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H98" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I98" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="J98" s="22" t="n">
-        <v>4873</v>
-      </c>
-      <c r="K98" s="22" t="n">
-        <v>1692</v>
-      </c>
-      <c r="L98" s="22" t="n">
-        <v>37234</v>
-      </c>
-      <c r="M98" s="22" t="n">
-        <v>76927</v>
-      </c>
-      <c r="N98" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="T98" s="22" t="n">
-        <v>66</v>
-      </c>
-      <c r="U98" s="22" t="n">
-        <v>886</v>
-      </c>
-      <c r="V98" s="22" t="n">
-        <v>10828</v>
-      </c>
-      <c r="W98" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="X98" s="22" t="n">
-        <v>76927</v>
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G98" s="17">
+        <f>IF(OR(G97="",C97=""),"",IF(C97&lt;=0,"",IFERROR(G97/C97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(OR(H97="",D97=""),"",IF(D97&lt;=0,"",IFERROR(H97/D97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I98" s="17">
+        <f>IF(OR(I97="",E97=""),"",IF(E97&lt;=0,"",IFERROR(I97/E97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J98" s="17">
+        <f>IF(OR(J97="",F97=""),"",IF(F97&lt;=0,"",IFERROR(J97/F97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T98" s="17">
+        <f>IF(OR(T97="",S97=""),"",IF(S97&lt;=0,"",IFERROR(T97/S97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U98" s="17">
+        <f>IF(OR(U97="",T97=""),"",IF(T97&lt;=0,"",IFERROR(U97/T97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V98" s="17">
+        <f>IF(OR(V97="",U97=""),"",IF(U97&lt;=0,"",IFERROR(V97/U97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W98" s="17">
+        <f>IF(OR(W97="",V97=""),"",IF(V97&lt;=0,"",IFERROR(W97/V97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손실</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="D99" s="22" t="n">
-        <v>240</v>
-      </c>
-      <c r="E99" s="22" t="n">
-        <v>189</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>164</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>180</v>
+          <t>투자유가증권 매각이익</t>
+        </is>
       </c>
       <c r="H99" s="22" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="I99" s="22" t="n">
-        <v>748</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>254</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>94</v>
+        <v>37216</v>
       </c>
       <c r="M99" s="22" t="n">
-        <v>664</v>
-      </c>
-      <c r="N99" s="22" t="n">
-        <v>145</v>
-      </c>
-      <c r="T99" s="22" t="n">
-        <v>166</v>
-      </c>
-      <c r="U99" s="22" t="n">
-        <v>205</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>189</v>
+        <v>76610</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>748</v>
+        <v>0</v>
       </c>
       <c r="X99" s="22" t="n">
-        <v>664</v>
+        <v>76610</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>0</v>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H100" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <v>4868</v>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>316</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>316</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>Provision For Loss On Litigation EL</t>
-        </is>
+          <t>고정자산 매각이익</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>10607</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G101" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H101" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="N101" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="U101" s="22" t="n">
+        <v>886</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>10607</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X101" s="22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>122</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>240</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>189</v>
+          <t>Gain On Refund Of Value Added Tax EI</t>
+        </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>180</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>105</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>1196</v>
+        <v>0</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>254</v>
+        <v>4849</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>221</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>813</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>1596</v>
+        <v>0</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>145</v>
-      </c>
-      <c r="T102" s="22" t="n">
-        <v>280</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>204</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>189</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>1196</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>1596</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>98122</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>134443</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>157860</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>167248</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>153607</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>200106</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>185153</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>151966</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>161020</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>153322</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>281872</v>
-      </c>
-      <c r="N103" s="12" t="n">
-        <v>215495</v>
-      </c>
-      <c r="T103" s="12" t="n">
-        <v>168130</v>
-      </c>
-      <c r="U103" s="12" t="n">
-        <v>155638</v>
-      </c>
-      <c r="V103" s="12" t="n">
-        <v>157860</v>
-      </c>
-      <c r="W103" s="12" t="n">
-        <v>185153</v>
-      </c>
-      <c r="X103" s="12" t="n">
-        <v>281872</v>
+      <c r="A103" s="20" t="inlineStr">
+        <is>
+          <t>특별이익 합계</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="22" t="n">
+        <v>10828</v>
+      </c>
+      <c r="F103" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="G103" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H103" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>4873</v>
+      </c>
+      <c r="K103" s="22" t="n">
+        <v>1692</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <v>37234</v>
+      </c>
+      <c r="M103" s="22" t="n">
+        <v>76927</v>
+      </c>
+      <c r="N103" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>66</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>886</v>
+      </c>
+      <c r="V103" s="22" t="n">
+        <v>10828</v>
+      </c>
+      <c r="W103" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="X103" s="22" t="n">
+        <v>76927</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
+          <t>고정자산 제각·매각손실</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="n">
+        <v>122</v>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="E104" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>164</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>180</v>
+      </c>
+      <c r="H104" s="22" t="n">
+        <v>105</v>
+      </c>
+      <c r="I104" s="22" t="n">
+        <v>748</v>
+      </c>
+      <c r="J104" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="K104" s="22" t="n">
+        <v>221</v>
+      </c>
+      <c r="L104" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="M104" s="22" t="n">
+        <v>664</v>
+      </c>
+      <c r="N104" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="T104" s="22" t="n">
+        <v>166</v>
+      </c>
+      <c r="U104" s="22" t="n">
+        <v>205</v>
+      </c>
+      <c r="V104" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="W104" s="22" t="n">
+        <v>748</v>
+      </c>
+      <c r="X104" s="22" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>Provision For Loss On Litigation EL</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>122</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>240</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>164</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>180</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>105</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>1196</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>254</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>221</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>813</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>1596</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>204</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>1196</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>98122</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>134443</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>157860</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>167248</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>153607</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>200106</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>185153</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>151966</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>161020</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>153322</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>281872</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>215495</v>
+      </c>
+      <c r="T108" s="12" t="n">
+        <v>168130</v>
+      </c>
+      <c r="U108" s="12" t="n">
+        <v>155638</v>
+      </c>
+      <c r="V108" s="12" t="n">
+        <v>157860</v>
+      </c>
+      <c r="W108" s="12" t="n">
+        <v>185153</v>
+      </c>
+      <c r="X108" s="12" t="n">
+        <v>281872</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
           <t>법인세 등</t>
         </is>
       </c>
-      <c r="C104" s="22" t="n">
+      <c r="C109" s="22" t="n">
         <v>24943</v>
       </c>
-      <c r="D104" s="22" t="n">
+      <c r="D109" s="22" t="n">
         <v>32911</v>
       </c>
-      <c r="E104" s="22" t="n">
+      <c r="E109" s="22" t="n">
         <v>32920</v>
       </c>
-      <c r="F104" s="22" t="n">
+      <c r="F109" s="22" t="n">
         <v>41059</v>
       </c>
-      <c r="G104" s="22" t="n">
+      <c r="G109" s="22" t="n">
         <v>35893</v>
       </c>
-      <c r="H104" s="22" t="n">
+      <c r="H109" s="22" t="n">
         <v>42842</v>
       </c>
-      <c r="I104" s="22" t="n">
+      <c r="I109" s="22" t="n">
         <v>42186</v>
       </c>
-      <c r="J104" s="22" t="n">
+      <c r="J109" s="22" t="n">
         <v>34165</v>
       </c>
-      <c r="K104" s="22" t="n">
+      <c r="K109" s="22" t="n">
         <v>37195</v>
       </c>
-      <c r="L104" s="22" t="n">
+      <c r="L109" s="22" t="n">
         <v>34783</v>
       </c>
-      <c r="M104" s="22" t="n">
+      <c r="M109" s="22" t="n">
         <v>67583</v>
       </c>
-      <c r="N104" s="22" t="n">
+      <c r="N109" s="22" t="n">
         <v>51153</v>
       </c>
-      <c r="T104" s="22" t="n">
+      <c r="T109" s="22" t="n">
         <v>41300</v>
       </c>
-      <c r="U104" s="22" t="n">
+      <c r="U109" s="22" t="n">
         <v>36975</v>
       </c>
-      <c r="V104" s="22" t="n">
+      <c r="V109" s="22" t="n">
         <v>32920</v>
       </c>
-      <c r="W104" s="22" t="n">
+      <c r="W109" s="22" t="n">
         <v>42186</v>
       </c>
-      <c r="X104" s="22" t="n">
+      <c r="X109" s="22" t="n">
         <v>67583</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>73179</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>101533</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>124939</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>126189</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>117714</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>157264</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>142966</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>117801</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>123825</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>118538</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>214290</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>164341</v>
-      </c>
-      <c r="T105" s="12" t="n">
-        <v>126830</v>
-      </c>
-      <c r="U105" s="12" t="n">
-        <v>118664</v>
-      </c>
-      <c r="V105" s="12" t="n">
-        <v>124939</v>
-      </c>
-      <c r="W105" s="12" t="n">
-        <v>142966</v>
-      </c>
-      <c r="X105" s="12" t="n">
-        <v>214290</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 순이익</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>73179</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>101533</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>124939</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>126189</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>117714</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>157264</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>142966</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>117801</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>123825</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>118538</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>214290</v>
-      </c>
-      <c r="N106" s="12" t="n">
-        <v>164341</v>
-      </c>
-      <c r="T106" s="12" t="n">
-        <v>126830</v>
-      </c>
-      <c r="U106" s="12" t="n">
-        <v>118664</v>
-      </c>
-      <c r="V106" s="12" t="n">
-        <v>124939</v>
-      </c>
-      <c r="W106" s="12" t="n">
-        <v>142966</v>
-      </c>
-      <c r="X106" s="12" t="n">
-        <v>214290</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B108" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-      <c r="J108" s="18" t="n"/>
-      <c r="K108" s="18" t="n"/>
-      <c r="L108" s="18" t="n"/>
-      <c r="M108" s="18" t="n"/>
-      <c r="N108" s="18" t="n"/>
-      <c r="O108" s="18" t="n"/>
-      <c r="P108" s="18" t="n"/>
-      <c r="Q108" s="18" t="n"/>
-      <c r="R108" s="18" t="n"/>
-      <c r="S108" s="18" t="n"/>
-      <c r="T108" s="18" t="n"/>
-      <c r="U108" s="18" t="n"/>
-      <c r="V108" s="18" t="n"/>
-      <c r="W108" s="18" t="n"/>
-      <c r="X108" s="18" t="n"/>
-      <c r="Y108" s="18" t="n"/>
-      <c r="Z108" s="18" t="n"/>
-      <c r="AA108" s="18" t="n"/>
-      <c r="AB108" s="18" t="n"/>
-      <c r="AC108" s="18" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M109" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N109" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O109" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P109" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q109" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R109" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S109" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T109" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U109" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V109" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W109" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X109" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y109" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z109" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA109" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB109" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC109" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
       </c>
     </row>
     <row r="110">
@@ -7462,2438 +7503,2868 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>2354</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>21157</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>37153</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>59097</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>-61664</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>-5990</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>-46769</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>45860</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>-3591</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>-13201</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>-10684</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>80612</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>-10735</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>41286</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>37153</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-46769</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>-10684</v>
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G111" s="17">
+        <f>IF(OR(G110="",C110=""),"",IF(C110&lt;=0,"",IFERROR(G110/C110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(OR(H110="",D110=""),"",IF(D110&lt;=0,"",IFERROR(H110/D110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I111" s="17">
+        <f>IF(OR(I110="",E110=""),"",IF(E110&lt;=0,"",IFERROR(I110/E110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>IF(OR(J110="",F110=""),"",IF(F110&lt;=0,"",IFERROR(J110/F110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF(OR(K110="",G110=""),"",IF(G110&lt;=0,"",IFERROR(K110/G110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L111" s="17">
+        <f>IF(OR(L110="",H110=""),"",IF(H110&lt;=0,"",IFERROR(L110/H110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M111" s="17">
+        <f>IF(OR(M110="",I110=""),"",IF(I110&lt;=0,"",IFERROR(M110/I110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="17">
+        <f>IF(OR(N110="",J110=""),"",IF(J110&lt;=0,"",IFERROR(N110/J110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T111" s="17">
+        <f>IF(OR(T110="",S110=""),"",IF(S110&lt;=0,"",IFERROR(T110/S110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U111" s="17">
+        <f>IF(OR(U110="",T110=""),"",IF(T110&lt;=0,"",IFERROR(U110/T110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V111" s="17">
+        <f>IF(OR(V110="",U110=""),"",IF(U110&lt;=0,"",IFERROR(V110/U110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W111" s="17">
+        <f>IF(OR(W110="",V110=""),"",IF(V110&lt;=0,"",IFERROR(W110/V110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X111" s="17">
+        <f>IF(OR(X110="",W110=""),"",IF(W110&lt;=0,"",IFERROR(X110/W110-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="n">
-        <v>5009</v>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>-7213</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>12570</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>16972</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>-29637</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>18761</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>-17570</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>5408</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>4518</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>15518</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>119</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>5696</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>12735</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>1517</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>12570</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-17570</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>119</v>
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>73179</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>101533</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>124939</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>126189</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>117714</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>157264</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>142966</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>117801</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>123825</v>
+      </c>
+      <c r="L112" s="12" t="n">
+        <v>118538</v>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>214290</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>164341</v>
+      </c>
+      <c r="T112" s="12" t="n">
+        <v>126830</v>
+      </c>
+      <c r="U112" s="12" t="n">
+        <v>118664</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>124939</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>142966</v>
+      </c>
+      <c r="X112" s="12" t="n">
+        <v>214290</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>-378</v>
-      </c>
-      <c r="D113" s="22" t="n">
-        <v>605</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>7801</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>-948</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>-828</v>
-      </c>
-      <c r="H113" s="22" t="n">
-        <v>-951</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>1322</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>-1065</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>-938</v>
-      </c>
-      <c r="L113" s="22" t="n">
-        <v>-1011</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>8753</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>-1493</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>1052</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>3674</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>7801</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>1322</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>8753</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>지분법 적용회사 지분 해당액</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>144</v>
-      </c>
-      <c r="D114" s="22" t="n">
-        <v>-31</v>
-      </c>
-      <c r="E114" s="22" t="n">
-        <v>94</v>
-      </c>
-      <c r="F114" s="22" t="n">
-        <v>143</v>
-      </c>
-      <c r="G114" s="22" t="n">
-        <v>-272</v>
-      </c>
-      <c r="H114" s="22" t="n">
-        <v>110</v>
-      </c>
-      <c r="I114" s="22" t="n">
-        <v>187</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>-213</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>44</v>
-      </c>
-      <c r="L114" s="22" t="n">
-        <v>113</v>
-      </c>
-      <c r="M114" s="22" t="n">
-        <v>249</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>31</v>
-      </c>
-      <c r="T114" s="22" t="n">
-        <v>-16</v>
-      </c>
-      <c r="U114" s="22" t="n">
-        <v>-29</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>94</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>187</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>249</v>
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G113" s="17">
+        <f>IF(OR(G112="",C112=""),"",IF(C112&lt;=0,"",IFERROR(G112/C112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(OR(H112="",D112=""),"",IF(D112&lt;=0,"",IFERROR(H112/D112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I113" s="17">
+        <f>IF(OR(I112="",E112=""),"",IF(E112&lt;=0,"",IFERROR(I112/E112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>IF(OR(J112="",F112=""),"",IF(F112&lt;=0,"",IFERROR(J112/F112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF(OR(K112="",G112=""),"",IF(G112&lt;=0,"",IFERROR(K112/G112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L113" s="17">
+        <f>IF(OR(L112="",H112=""),"",IF(H112&lt;=0,"",IFERROR(L112/H112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M113" s="17">
+        <f>IF(OR(M112="",I112=""),"",IF(I112&lt;=0,"",IFERROR(M112/I112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="17">
+        <f>IF(OR(N112="",J112=""),"",IF(J112&lt;=0,"",IFERROR(N112/J112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T113" s="17">
+        <f>IF(OR(T112="",S112=""),"",IF(S112&lt;=0,"",IFERROR(T112/S112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U113" s="17">
+        <f>IF(OR(U112="",T112=""),"",IF(T112&lt;=0,"",IFERROR(U112/T112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V113" s="17">
+        <f>IF(OR(V112="",U112=""),"",IF(U112&lt;=0,"",IFERROR(V112/U112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W113" s="17">
+        <f>IF(OR(W112="",V112=""),"",IF(V112&lt;=0,"",IFERROR(W112/V112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X113" s="17">
+        <f>IF(OR(X112="",W112=""),"",IF(W112&lt;=0,"",IFERROR(X112/W112-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>7129</v>
-      </c>
-      <c r="D115" s="22" t="n">
-        <v>14518</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>57620</v>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>75264</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>-92402</v>
-      </c>
-      <c r="H115" s="22" t="n">
-        <v>11931</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>-62831</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>49990</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="L115" s="22" t="n">
-        <v>1419</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>-1560</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>84846</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>3038</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>46449</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>57620</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>-62831</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>-1560</v>
-      </c>
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B115" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="18" t="n"/>
+      <c r="L115" s="18" t="n"/>
+      <c r="M115" s="18" t="n"/>
+      <c r="N115" s="18" t="n"/>
+      <c r="O115" s="18" t="n"/>
+      <c r="P115" s="18" t="n"/>
+      <c r="Q115" s="18" t="n"/>
+      <c r="R115" s="18" t="n"/>
+      <c r="S115" s="18" t="n"/>
+      <c r="T115" s="18" t="n"/>
+      <c r="U115" s="18" t="n"/>
+      <c r="V115" s="18" t="n"/>
+      <c r="W115" s="18" t="n"/>
+      <c r="X115" s="18" t="n"/>
+      <c r="Y115" s="18" t="n"/>
+      <c r="Z115" s="18" t="n"/>
+      <c r="AA115" s="18" t="n"/>
+      <c r="AB115" s="18" t="n"/>
+      <c r="AC115" s="18" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>80308</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>116050</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>182559</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>201454</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>25310</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>169195</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>80136</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>167791</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>123857</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>119958</v>
-      </c>
-      <c r="M116" s="12" t="n">
-        <v>212729</v>
-      </c>
-      <c r="N116" s="12" t="n">
-        <v>249188</v>
-      </c>
-      <c r="T116" s="12" t="n">
-        <v>129867</v>
-      </c>
-      <c r="U116" s="12" t="n">
-        <v>165113</v>
-      </c>
-      <c r="V116" s="12" t="n">
-        <v>182559</v>
-      </c>
-      <c r="W116" s="12" t="n">
-        <v>80136</v>
-      </c>
-      <c r="X116" s="12" t="n">
-        <v>212729</v>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P116" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q116" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R116" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S116" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T116" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U116" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V116" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W116" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X116" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y116" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z116" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA116" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB116" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC116" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>지배주주 포괄이익</t>
+          <t>순이익</t>
         </is>
       </c>
       <c r="C117" s="12" t="n">
-        <v>80308</v>
+        <v>73179</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>116050</v>
+        <v>101533</v>
       </c>
       <c r="E117" s="12" t="n">
-        <v>182559</v>
+        <v>124939</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>201454</v>
+        <v>126189</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>25310</v>
+        <v>117714</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>169195</v>
+        <v>157264</v>
       </c>
       <c r="I117" s="12" t="n">
-        <v>80136</v>
+        <v>142966</v>
       </c>
       <c r="J117" s="12" t="n">
-        <v>167791</v>
+        <v>117801</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>123857</v>
+        <v>123825</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>119958</v>
+        <v>118538</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>212729</v>
+        <v>214290</v>
       </c>
       <c r="N117" s="12" t="n">
-        <v>249188</v>
+        <v>164341</v>
       </c>
       <c r="T117" s="12" t="n">
-        <v>129867</v>
+        <v>126830</v>
       </c>
       <c r="U117" s="12" t="n">
-        <v>165113</v>
+        <v>118664</v>
       </c>
       <c r="V117" s="12" t="n">
-        <v>182559</v>
+        <v>124939</v>
       </c>
       <c r="W117" s="12" t="n">
-        <v>80136</v>
+        <v>142966</v>
       </c>
       <c r="X117" s="12" t="n">
-        <v>212729</v>
+        <v>214290</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="n">
+        <v>2354</v>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>21157</v>
+      </c>
+      <c r="E118" s="22" t="n">
+        <v>37153</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>59097</v>
+      </c>
+      <c r="G118" s="22" t="n">
+        <v>-61664</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>-5990</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>-46769</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>45860</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>-3591</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>-13201</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>-10684</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>80612</v>
+      </c>
+      <c r="T118" s="22" t="n">
+        <v>-10735</v>
+      </c>
+      <c r="U118" s="22" t="n">
+        <v>41286</v>
+      </c>
+      <c r="V118" s="22" t="n">
+        <v>37153</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>-46769</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>-10684</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B119" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-      <c r="J119" s="18" t="n"/>
-      <c r="K119" s="18" t="n"/>
-      <c r="L119" s="18" t="n"/>
-      <c r="M119" s="18" t="n"/>
-      <c r="N119" s="18" t="n"/>
-      <c r="O119" s="18" t="n"/>
-      <c r="P119" s="18" t="n"/>
-      <c r="Q119" s="18" t="n"/>
-      <c r="R119" s="18" t="n"/>
-      <c r="S119" s="18" t="n"/>
-      <c r="T119" s="18" t="n"/>
-      <c r="U119" s="18" t="n"/>
-      <c r="V119" s="18" t="n"/>
-      <c r="W119" s="18" t="n"/>
-      <c r="X119" s="18" t="n"/>
-      <c r="Y119" s="18" t="n"/>
-      <c r="Z119" s="18" t="n"/>
-      <c r="AA119" s="18" t="n"/>
-      <c r="AB119" s="18" t="n"/>
-      <c r="AC119" s="18" t="n"/>
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>5009</v>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>-7213</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>12570</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>16972</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>-29637</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>18761</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>-17570</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>5408</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>4518</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>15518</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>119</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>5696</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>12735</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>1517</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>12570</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>-17570</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H120" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I120" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N120" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O120" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P120" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q120" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R120" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S120" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T120" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U120" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V120" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W120" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X120" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y120" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z120" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA120" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB120" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC120" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n">
+        <v>-378</v>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>605</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>7801</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>-948</v>
+      </c>
+      <c r="G120" s="22" t="n">
+        <v>-828</v>
+      </c>
+      <c r="H120" s="22" t="n">
+        <v>-951</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>1322</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>-1065</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>-938</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <v>-1011</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <v>8753</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>-1493</v>
+      </c>
+      <c r="T120" s="22" t="n">
+        <v>1052</v>
+      </c>
+      <c r="U120" s="22" t="n">
+        <v>3674</v>
+      </c>
+      <c r="V120" s="22" t="n">
+        <v>7801</v>
+      </c>
+      <c r="W120" s="22" t="n">
+        <v>1322</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>8753</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>181136</v>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v>473439</v>
-      </c>
-      <c r="G121" s="12" t="n">
-        <v>320855</v>
-      </c>
-      <c r="I121" s="12" t="n">
-        <v>706114</v>
-      </c>
-      <c r="K121" s="12" t="n">
-        <v>312986</v>
-      </c>
-      <c r="M121" s="12" t="n">
-        <v>748180</v>
-      </c>
-      <c r="O121" s="12" t="n">
-        <v>149116</v>
-      </c>
-      <c r="P121" s="12" t="n">
-        <v>275242</v>
-      </c>
-      <c r="Q121" s="12" t="n">
-        <v>321508</v>
-      </c>
-      <c r="R121" s="12" t="n">
-        <v>244626</v>
-      </c>
-      <c r="S121" s="12" t="n">
-        <v>317038</v>
-      </c>
-      <c r="T121" s="12" t="n">
-        <v>596698</v>
-      </c>
-      <c r="U121" s="12" t="n">
-        <v>624856</v>
-      </c>
-      <c r="V121" s="12" t="n">
-        <v>473439</v>
-      </c>
-      <c r="W121" s="12" t="n">
-        <v>706114</v>
-      </c>
-      <c r="X121" s="12" t="n">
-        <v>748180</v>
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>지분법 적용회사 지분 해당액</t>
+        </is>
+      </c>
+      <c r="C121" s="22" t="n">
+        <v>144</v>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>-31</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>143</v>
+      </c>
+      <c r="G121" s="22" t="n">
+        <v>-272</v>
+      </c>
+      <c r="H121" s="22" t="n">
+        <v>110</v>
+      </c>
+      <c r="I121" s="22" t="n">
+        <v>187</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>-213</v>
+      </c>
+      <c r="K121" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="L121" s="22" t="n">
+        <v>113</v>
+      </c>
+      <c r="M121" s="22" t="n">
+        <v>249</v>
+      </c>
+      <c r="N121" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="T121" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="U121" s="22" t="n">
+        <v>-29</v>
+      </c>
+      <c r="V121" s="22" t="n">
+        <v>94</v>
+      </c>
+      <c r="W121" s="22" t="n">
+        <v>187</v>
+      </c>
+      <c r="X121" s="22" t="n">
+        <v>249</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>기타포괄손익 합계</t>
         </is>
       </c>
       <c r="C122" s="22" t="n">
-        <v>23185</v>
+        <v>7129</v>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>14518</v>
       </c>
       <c r="E122" s="22" t="n">
-        <v>52339</v>
+        <v>57620</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>75264</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>27709</v>
+        <v>-92402</v>
+      </c>
+      <c r="H122" s="22" t="n">
+        <v>11931</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>62148</v>
+        <v>-62831</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>49990</v>
       </c>
       <c r="K122" s="22" t="n">
-        <v>36279</v>
+        <v>32</v>
+      </c>
+      <c r="L122" s="22" t="n">
+        <v>1419</v>
       </c>
       <c r="M122" s="22" t="n">
-        <v>80982</v>
-      </c>
-      <c r="O122" s="22" t="n">
-        <v>17872</v>
-      </c>
-      <c r="P122" s="22" t="n">
-        <v>20619</v>
-      </c>
-      <c r="Q122" s="22" t="n">
-        <v>24323</v>
-      </c>
-      <c r="R122" s="22" t="n">
-        <v>29107</v>
-      </c>
-      <c r="S122" s="22" t="n">
-        <v>33843</v>
+        <v>-1560</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>84846</v>
       </c>
       <c r="T122" s="22" t="n">
-        <v>36727</v>
+        <v>3038</v>
       </c>
       <c r="U122" s="22" t="n">
-        <v>42927</v>
+        <v>46449</v>
       </c>
       <c r="V122" s="22" t="n">
-        <v>52339</v>
+        <v>57620</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>62148</v>
+        <v>-62831</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>80982</v>
+        <v>-1560</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="O123" s="22" t="n">
-        <v>362</v>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>925</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>0</v>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>80308</v>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>116050</v>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>182559</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>201454</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>25310</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>169195</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>80136</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>167791</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>123857</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>119958</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>212729</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>249188</v>
+      </c>
+      <c r="T123" s="12" t="n">
+        <v>129867</v>
+      </c>
+      <c r="U123" s="12" t="n">
+        <v>165113</v>
+      </c>
+      <c r="V123" s="12" t="n">
+        <v>182559</v>
+      </c>
+      <c r="W123" s="12" t="n">
+        <v>80136</v>
+      </c>
+      <c r="X123" s="12" t="n">
+        <v>212729</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C124" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="E124" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="G124" s="22" t="n">
-        <v>54</v>
-      </c>
-      <c r="I124" s="22" t="n">
-        <v>117</v>
-      </c>
-      <c r="K124" s="22" t="n">
-        <v>183</v>
-      </c>
-      <c r="M124" s="22" t="n">
-        <v>363</v>
-      </c>
-      <c r="O124" s="22" t="n">
-        <v>631</v>
-      </c>
-      <c r="P124" s="22" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>354</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>196</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>199</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>206</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>168</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>117</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="n">
-        <v>-19156</v>
-      </c>
-      <c r="E125" s="22" t="n">
-        <v>-631</v>
-      </c>
-      <c r="G125" s="22" t="n">
-        <v>-6653</v>
-      </c>
-      <c r="I125" s="22" t="n">
-        <v>11784</v>
-      </c>
-      <c r="K125" s="22" t="n">
-        <v>-21858</v>
-      </c>
-      <c r="M125" s="22" t="n">
-        <v>-17769</v>
-      </c>
-      <c r="O125" s="22" t="n">
-        <v>10112</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>12710</v>
-      </c>
-      <c r="Q125" s="22" t="n">
-        <v>-1165</v>
-      </c>
-      <c r="R125" s="22" t="n">
-        <v>-3802</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>4612</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>9540</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>-2301</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>-631</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>11784</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>-17769</v>
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>80308</v>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>116050</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>182559</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>201454</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>25310</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>169195</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>80136</v>
+      </c>
+      <c r="J124" s="12" t="n">
+        <v>167791</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>123857</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>119958</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>212729</v>
+      </c>
+      <c r="N124" s="12" t="n">
+        <v>249188</v>
+      </c>
+      <c r="T124" s="12" t="n">
+        <v>129867</v>
+      </c>
+      <c r="U124" s="12" t="n">
+        <v>165113</v>
+      </c>
+      <c r="V124" s="12" t="n">
+        <v>182559</v>
+      </c>
+      <c r="W124" s="12" t="n">
+        <v>80136</v>
+      </c>
+      <c r="X124" s="12" t="n">
+        <v>212729</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="O126" s="22" t="n">
-        <v>623</v>
-      </c>
-      <c r="P126" s="22" t="n">
-        <v>2573</v>
-      </c>
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B126" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+      <c r="J126" s="18" t="n"/>
+      <c r="K126" s="18" t="n"/>
+      <c r="L126" s="18" t="n"/>
+      <c r="M126" s="18" t="n"/>
+      <c r="N126" s="18" t="n"/>
+      <c r="O126" s="18" t="n"/>
+      <c r="P126" s="18" t="n"/>
+      <c r="Q126" s="18" t="n"/>
+      <c r="R126" s="18" t="n"/>
+      <c r="S126" s="18" t="n"/>
+      <c r="T126" s="18" t="n"/>
+      <c r="U126" s="18" t="n"/>
+      <c r="V126" s="18" t="n"/>
+      <c r="W126" s="18" t="n"/>
+      <c r="X126" s="18" t="n"/>
+      <c r="Y126" s="18" t="n"/>
+      <c r="Z126" s="18" t="n"/>
+      <c r="AA126" s="18" t="n"/>
+      <c r="AB126" s="18" t="n"/>
+      <c r="AC126" s="18" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>제품보증 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C127" s="22" t="n">
-        <v>-1761</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>2493</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>6869</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>-1321</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>-61</v>
-      </c>
-      <c r="O127" s="22" t="n">
-        <v>-220</v>
-      </c>
-      <c r="P127" s="22" t="n">
-        <v>2769</v>
-      </c>
-      <c r="Q127" s="22" t="n">
-        <v>2968</v>
-      </c>
-      <c r="S127" s="22" t="n">
-        <v>-176</v>
-      </c>
-      <c r="T127" s="22" t="n">
-        <v>9614</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>7594</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>-1271</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>6869</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>-61</v>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R127" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S127" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T127" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U127" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V127" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W127" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X127" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y127" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z127" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA127" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB127" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC127" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>관계회사 정리손실 충당금 전입</t>
-        </is>
-      </c>
-      <c r="R128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="22" t="n">
-        <v>3327</v>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>0</v>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>181136</v>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>473439</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>320855</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>706114</v>
+      </c>
+      <c r="K128" s="12" t="n">
+        <v>312986</v>
+      </c>
+      <c r="M128" s="12" t="n">
+        <v>748180</v>
+      </c>
+      <c r="O128" s="12" t="n">
+        <v>149116</v>
+      </c>
+      <c r="P128" s="12" t="n">
+        <v>275242</v>
+      </c>
+      <c r="Q128" s="12" t="n">
+        <v>321508</v>
+      </c>
+      <c r="R128" s="12" t="n">
+        <v>244626</v>
+      </c>
+      <c r="S128" s="12" t="n">
+        <v>317038</v>
+      </c>
+      <c r="T128" s="12" t="n">
+        <v>596698</v>
+      </c>
+      <c r="U128" s="12" t="n">
+        <v>624856</v>
+      </c>
+      <c r="V128" s="12" t="n">
+        <v>473439</v>
+      </c>
+      <c r="W128" s="12" t="n">
+        <v>706114</v>
+      </c>
+      <c r="X128" s="12" t="n">
+        <v>748180</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n">
+        <v>23185</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>52339</v>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>27709</v>
+      </c>
+      <c r="I129" s="22" t="n">
+        <v>62148</v>
+      </c>
+      <c r="K129" s="22" t="n">
+        <v>36279</v>
+      </c>
+      <c r="M129" s="22" t="n">
+        <v>80982</v>
       </c>
       <c r="O129" s="22" t="n">
-        <v>-17411</v>
+        <v>17872</v>
       </c>
       <c r="P129" s="22" t="n">
-        <v>-25971</v>
+        <v>20619</v>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>10541</v>
+        <v>24323</v>
       </c>
       <c r="R129" s="22" t="n">
-        <v>-5370</v>
+        <v>29107</v>
       </c>
       <c r="S129" s="22" t="n">
-        <v>-37736</v>
+        <v>33843</v>
       </c>
       <c r="T129" s="22" t="n">
-        <v>0</v>
+        <v>36727</v>
+      </c>
+      <c r="U129" s="22" t="n">
+        <v>42927</v>
+      </c>
+      <c r="V129" s="22" t="n">
+        <v>52339</v>
+      </c>
+      <c r="W129" s="22" t="n">
+        <v>62148</v>
+      </c>
+      <c r="X129" s="22" t="n">
+        <v>80982</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="S130" s="22" t="n">
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="O130" s="22" t="n">
+        <v>362</v>
+      </c>
+      <c r="P130" s="22" t="n">
+        <v>925</v>
+      </c>
+      <c r="Q130" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="T130" s="22" t="n">
-        <v>-195543</v>
-      </c>
-      <c r="U130" s="22" t="n">
-        <v>-24750</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
-        <v>106472</v>
+        <v>36</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>117</v>
+      </c>
+      <c r="K131" s="22" t="n">
+        <v>183</v>
+      </c>
+      <c r="M131" s="22" t="n">
+        <v>363</v>
+      </c>
+      <c r="O131" s="22" t="n">
+        <v>631</v>
+      </c>
+      <c r="P131" s="22" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>354</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>196</v>
+      </c>
+      <c r="S131" s="22" t="n">
+        <v>199</v>
+      </c>
+      <c r="T131" s="22" t="n">
+        <v>206</v>
+      </c>
+      <c r="U131" s="22" t="n">
+        <v>168</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>73</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>117</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>363</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="n">
+        <v>-19156</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-3737</v>
+        <v>-631</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>-2751</v>
+        <v>-6653</v>
       </c>
       <c r="I132" s="22" t="n">
-        <v>-3580</v>
+        <v>11784</v>
       </c>
       <c r="K132" s="22" t="n">
-        <v>-2368</v>
+        <v>-21858</v>
       </c>
       <c r="M132" s="22" t="n">
-        <v>-3448</v>
+        <v>-17769</v>
       </c>
       <c r="O132" s="22" t="n">
-        <v>-1032</v>
+        <v>10112</v>
       </c>
       <c r="P132" s="22" t="n">
-        <v>-859</v>
+        <v>12710</v>
       </c>
       <c r="Q132" s="22" t="n">
-        <v>-2573</v>
+        <v>-1165</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>-1920</v>
+        <v>-3802</v>
+      </c>
+      <c r="S132" s="22" t="n">
+        <v>4612</v>
+      </c>
+      <c r="T132" s="22" t="n">
+        <v>9540</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-2435</v>
+        <v>-2301</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-3737</v>
+        <v>-631</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-3580</v>
+        <v>11784</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>-3448</v>
+        <v>-17769</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손익</t>
-        </is>
-      </c>
-      <c r="E133" s="22" t="n">
-        <v>-10032</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>-109</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>-10032</v>
+          <t>임원 상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="O133" s="22" t="n">
+        <v>623</v>
+      </c>
+      <c r="P133" s="22" t="n">
+        <v>2573</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
-        </is>
+          <t>제품보증 충당금 증감</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="n">
+        <v>-1761</v>
+      </c>
+      <c r="E134" s="22" t="n">
+        <v>-1271</v>
+      </c>
+      <c r="G134" s="22" t="n">
+        <v>2493</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>-1046</v>
+        <v>6869</v>
+      </c>
+      <c r="K134" s="22" t="n">
+        <v>-1321</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-115494</v>
+        <v>-61</v>
+      </c>
+      <c r="O134" s="22" t="n">
+        <v>-220</v>
+      </c>
+      <c r="P134" s="22" t="n">
+        <v>2769</v>
+      </c>
+      <c r="Q134" s="22" t="n">
+        <v>2968</v>
+      </c>
+      <c r="S134" s="22" t="n">
+        <v>-176</v>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>9614</v>
+      </c>
+      <c r="U134" s="22" t="n">
+        <v>7594</v>
+      </c>
+      <c r="V134" s="22" t="n">
+        <v>-1271</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>-1046</v>
+        <v>6869</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>-115494</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="C135" s="22" t="n">
-        <v>106472</v>
-      </c>
-      <c r="E135" s="22" t="n">
-        <v>84848</v>
-      </c>
-      <c r="G135" s="22" t="n">
-        <v>15788</v>
-      </c>
-      <c r="I135" s="22" t="n">
-        <v>-97519</v>
-      </c>
-      <c r="K135" s="22" t="n">
-        <v>77979</v>
-      </c>
-      <c r="M135" s="22" t="n">
-        <v>-29900</v>
-      </c>
-      <c r="U135" s="22" t="n">
-        <v>-24750</v>
-      </c>
-      <c r="V135" s="22" t="n">
-        <v>84848</v>
-      </c>
-      <c r="W135" s="22" t="n">
-        <v>-97519</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>-29900</v>
+          <t>관계회사 정리손실 충당금 전입</t>
+        </is>
+      </c>
+      <c r="R135" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="22" t="n">
+        <v>3327</v>
+      </c>
+      <c r="T135" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="C136" s="22" t="n">
-        <v>-85346</v>
-      </c>
-      <c r="E136" s="22" t="n">
-        <v>-97712</v>
-      </c>
-      <c r="G136" s="22" t="n">
-        <v>15265</v>
-      </c>
-      <c r="I136" s="22" t="n">
-        <v>8485</v>
-      </c>
-      <c r="K136" s="22" t="n">
-        <v>33349</v>
-      </c>
-      <c r="M136" s="22" t="n">
-        <v>47957</v>
+          <t>매출채권 증감</t>
+        </is>
       </c>
       <c r="O136" s="22" t="n">
-        <v>-44102</v>
+        <v>-17411</v>
       </c>
       <c r="P136" s="22" t="n">
-        <v>-109846</v>
+        <v>-25971</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>-14765</v>
+        <v>10541</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>-44065</v>
+        <v>-5370</v>
       </c>
       <c r="S136" s="22" t="n">
-        <v>-17226</v>
+        <v>-37736</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>-100309</v>
-      </c>
-      <c r="U136" s="22" t="n">
-        <v>-173487</v>
-      </c>
-      <c r="V136" s="22" t="n">
-        <v>-97712</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>8485</v>
-      </c>
-      <c r="X136" s="22" t="n">
-        <v>47957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="C137" s="22" t="n">
-        <v>-28588</v>
-      </c>
-      <c r="E137" s="22" t="n">
-        <v>-29629</v>
-      </c>
-      <c r="G137" s="22" t="n">
-        <v>8878</v>
-      </c>
-      <c r="I137" s="22" t="n">
-        <v>19512</v>
-      </c>
-      <c r="K137" s="22" t="n">
-        <v>-13918</v>
-      </c>
-      <c r="M137" s="22" t="n">
-        <v>14351</v>
-      </c>
-      <c r="O137" s="22" t="n">
-        <v>24053</v>
-      </c>
-      <c r="P137" s="22" t="n">
-        <v>28535</v>
-      </c>
-      <c r="Q137" s="22" t="n">
-        <v>-31752</v>
-      </c>
-      <c r="R137" s="22" t="n">
-        <v>22337</v>
+          <t>매출채권·계약자산 증감</t>
+        </is>
       </c>
       <c r="S137" s="22" t="n">
-        <v>-8255</v>
+        <v>0</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>18892</v>
+        <v>-195543</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-11406</v>
-      </c>
-      <c r="V137" s="22" t="n">
-        <v>-29629</v>
-      </c>
-      <c r="W137" s="22" t="n">
-        <v>19512</v>
-      </c>
-      <c r="X137" s="22" t="n">
-        <v>14351</v>
+        <v>-24750</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>미수 소비세 증감</t>
+          <t>매출채권·계약자산 증감</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>91166</v>
-      </c>
-      <c r="E138" s="22" t="n">
-        <v>88092</v>
-      </c>
-      <c r="G138" s="22" t="n">
-        <v>7005</v>
-      </c>
-      <c r="I138" s="22" t="n">
-        <v>2675</v>
-      </c>
-      <c r="K138" s="22" t="n">
-        <v>-2969</v>
-      </c>
-      <c r="M138" s="22" t="n">
-        <v>-7594</v>
-      </c>
-      <c r="O138" s="22" t="n">
-        <v>-12350</v>
-      </c>
-      <c r="P138" s="22" t="n">
-        <v>-13896</v>
-      </c>
-      <c r="Q138" s="22" t="n">
-        <v>6818</v>
-      </c>
-      <c r="R138" s="22" t="n">
-        <v>-19508</v>
-      </c>
-      <c r="S138" s="22" t="n">
-        <v>-13549</v>
-      </c>
-      <c r="T138" s="22" t="n">
-        <v>-27675</v>
-      </c>
-      <c r="U138" s="22" t="n">
-        <v>-13390</v>
-      </c>
-      <c r="V138" s="22" t="n">
-        <v>88092</v>
-      </c>
-      <c r="W138" s="22" t="n">
-        <v>2675</v>
-      </c>
-      <c r="X138" s="22" t="n">
-        <v>-7594</v>
+        <v>106472</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="C139" s="22" t="n">
-        <v>-3830</v>
+          <t>이자·배당금 수익</t>
+        </is>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-3639</v>
+        <v>-3737</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>13447</v>
+        <v>-2751</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>27100</v>
+        <v>-3580</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>-24184</v>
+        <v>-2368</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>-26066</v>
+        <v>-3448</v>
       </c>
       <c r="O139" s="22" t="n">
-        <v>359</v>
+        <v>-1032</v>
       </c>
       <c r="P139" s="22" t="n">
-        <v>1297</v>
+        <v>-859</v>
       </c>
       <c r="Q139" s="22" t="n">
-        <v>-2845</v>
+        <v>-2573</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>6140</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>-5699</v>
+        <v>-1920</v>
+      </c>
+      <c r="U139" s="22" t="n">
+        <v>-2435</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-3639</v>
+        <v>-3737</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>27100</v>
+        <v>-3580</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-26066</v>
+        <v>-3448</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
-        </is>
-      </c>
-      <c r="C140" s="22" t="n">
-        <v>18898</v>
+          <t>고정자산 제각·매각손익</t>
+        </is>
       </c>
       <c r="E140" s="22" t="n">
-        <v>-2390</v>
-      </c>
-      <c r="G140" s="22" t="n">
-        <v>8761</v>
-      </c>
-      <c r="I140" s="22" t="n">
-        <v>-32512</v>
-      </c>
-      <c r="K140" s="22" t="n">
-        <v>-33752</v>
-      </c>
-      <c r="M140" s="22" t="n">
-        <v>11426</v>
-      </c>
-      <c r="O140" s="22" t="n">
-        <v>34444</v>
-      </c>
-      <c r="P140" s="22" t="n">
-        <v>31684</v>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>-22077</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>58630</v>
-      </c>
-      <c r="S140" s="22" t="n">
-        <v>-54851</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>32031</v>
+        <v>-10032</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>185616</v>
+        <v>-109</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-2390</v>
-      </c>
-      <c r="W140" s="22" t="n">
-        <v>-32512</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>11426</v>
+        <v>-10032</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C141" s="22" t="n">
-        <v>-12397</v>
-      </c>
-      <c r="E141" s="22" t="n">
-        <v>-10671</v>
-      </c>
-      <c r="G141" s="22" t="n">
-        <v>-1706</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
       </c>
       <c r="I141" s="22" t="n">
-        <v>10365</v>
-      </c>
-      <c r="K141" s="22" t="n">
-        <v>-3915</v>
+        <v>-1046</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>11105</v>
-      </c>
-      <c r="O141" s="22" t="n">
-        <v>5843</v>
-      </c>
-      <c r="P141" s="22" t="n">
-        <v>24136</v>
-      </c>
-      <c r="Q141" s="22" t="n">
-        <v>1399</v>
-      </c>
-      <c r="R141" s="22" t="n">
-        <v>4387</v>
-      </c>
-      <c r="S141" s="22" t="n">
-        <v>4766</v>
-      </c>
-      <c r="T141" s="22" t="n">
-        <v>7070</v>
-      </c>
-      <c r="U141" s="22" t="n">
-        <v>-809</v>
-      </c>
-      <c r="V141" s="22" t="n">
-        <v>-10671</v>
+        <v>-115494</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>10365</v>
+        <v>-1046</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>11105</v>
+        <v>-115494</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>매출채권·계약자산 증감</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
-        <v>269814</v>
+        <v>106472</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>549109</v>
+        <v>84848</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>409148</v>
+        <v>15788</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>720516</v>
+        <v>-97519</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>356490</v>
+        <v>77979</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>714029</v>
-      </c>
-      <c r="O142" s="22" t="n">
-        <v>168304</v>
-      </c>
-      <c r="P142" s="22" t="n">
-        <v>235238</v>
-      </c>
-      <c r="Q142" s="22" t="n">
-        <v>289766</v>
-      </c>
-      <c r="R142" s="22" t="n">
-        <v>292679</v>
-      </c>
-      <c r="S142" s="22" t="n">
-        <v>231990</v>
-      </c>
-      <c r="T142" s="22" t="n">
-        <v>387252</v>
+        <v>-29900</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>632473</v>
+        <v>-24750</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>549109</v>
+        <v>84848</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>720516</v>
+        <v>-97519</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>714029</v>
+        <v>-29900</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>재고자산 증감</t>
         </is>
       </c>
       <c r="C143" s="22" t="n">
-        <v>2779</v>
+        <v>-85346</v>
       </c>
       <c r="E143" s="22" t="n">
-        <v>4546</v>
+        <v>-97712</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>3359</v>
+        <v>15265</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>4472</v>
+        <v>8485</v>
       </c>
       <c r="K143" s="22" t="n">
-        <v>2788</v>
+        <v>33349</v>
       </c>
       <c r="M143" s="22" t="n">
-        <v>4075</v>
+        <v>47957</v>
       </c>
       <c r="O143" s="22" t="n">
-        <v>1266</v>
+        <v>-44102</v>
       </c>
       <c r="P143" s="22" t="n">
-        <v>1115</v>
+        <v>-109846</v>
       </c>
       <c r="Q143" s="22" t="n">
-        <v>2738</v>
+        <v>-14765</v>
       </c>
       <c r="R143" s="22" t="n">
-        <v>2326</v>
+        <v>-44065</v>
       </c>
       <c r="S143" s="22" t="n">
-        <v>1669</v>
+        <v>-17226</v>
       </c>
       <c r="T143" s="22" t="n">
-        <v>2232</v>
+        <v>-100309</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>2907</v>
+        <v>-173487</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>4546</v>
+        <v>-97712</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>4472</v>
+        <v>8485</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>4075</v>
+        <v>47957</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>-71971</v>
+        <v>-28588</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>-118935</v>
+        <v>-29629</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-80074</v>
+        <v>8878</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-142814</v>
+        <v>19512</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-108429</v>
+        <v>-13918</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-178372</v>
+        <v>14351</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>-32622</v>
+        <v>24053</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-49771</v>
+        <v>28535</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-102932</v>
+        <v>-31752</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>-41888</v>
+        <v>22337</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>-87772</v>
+        <v>-8255</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-106098</v>
+        <v>18892</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-209111</v>
+        <v>-11406</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-118935</v>
+        <v>-29629</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-142814</v>
+        <v>19512</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-178372</v>
+        <v>14351</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C145" s="12" t="n">
-        <v>200622</v>
-      </c>
-      <c r="E145" s="12" t="n">
-        <v>434720</v>
-      </c>
-      <c r="G145" s="12" t="n">
-        <v>332433</v>
-      </c>
-      <c r="I145" s="12" t="n">
-        <v>582174</v>
-      </c>
-      <c r="K145" s="12" t="n">
-        <v>250848</v>
-      </c>
-      <c r="M145" s="12" t="n">
-        <v>539732</v>
-      </c>
-      <c r="O145" s="12" t="n">
-        <v>136948</v>
-      </c>
-      <c r="P145" s="12" t="n">
-        <v>186582</v>
-      </c>
-      <c r="Q145" s="12" t="n">
-        <v>189572</v>
-      </c>
-      <c r="R145" s="12" t="n">
-        <v>253117</v>
-      </c>
-      <c r="S145" s="12" t="n">
-        <v>145888</v>
-      </c>
-      <c r="T145" s="12" t="n">
-        <v>283387</v>
-      </c>
-      <c r="U145" s="12" t="n">
-        <v>426270</v>
-      </c>
-      <c r="V145" s="12" t="n">
-        <v>434720</v>
-      </c>
-      <c r="W145" s="12" t="n">
-        <v>582174</v>
-      </c>
-      <c r="X145" s="12" t="n">
-        <v>539732</v>
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>미수 소비세 증감</t>
+        </is>
+      </c>
+      <c r="C145" s="22" t="n">
+        <v>91166</v>
+      </c>
+      <c r="E145" s="22" t="n">
+        <v>88092</v>
+      </c>
+      <c r="G145" s="22" t="n">
+        <v>7005</v>
+      </c>
+      <c r="I145" s="22" t="n">
+        <v>2675</v>
+      </c>
+      <c r="K145" s="22" t="n">
+        <v>-2969</v>
+      </c>
+      <c r="M145" s="22" t="n">
+        <v>-7594</v>
+      </c>
+      <c r="O145" s="22" t="n">
+        <v>-12350</v>
+      </c>
+      <c r="P145" s="22" t="n">
+        <v>-13896</v>
+      </c>
+      <c r="Q145" s="22" t="n">
+        <v>6818</v>
+      </c>
+      <c r="R145" s="22" t="n">
+        <v>-19508</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>-13549</v>
+      </c>
+      <c r="T145" s="22" t="n">
+        <v>-27675</v>
+      </c>
+      <c r="U145" s="22" t="n">
+        <v>-13390</v>
+      </c>
+      <c r="V145" s="22" t="n">
+        <v>88092</v>
+      </c>
+      <c r="W145" s="22" t="n">
+        <v>2675</v>
+      </c>
+      <c r="X145" s="22" t="n">
+        <v>-7594</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>정기예금 증감</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
-        <v>-83</v>
+        <v>-3830</v>
+      </c>
+      <c r="E146" s="22" t="n">
+        <v>-3639</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>-4</v>
+        <v>13447</v>
+      </c>
+      <c r="I146" s="22" t="n">
+        <v>27100</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>-0</v>
+        <v>-24184</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>-26066</v>
+      </c>
+      <c r="O146" s="22" t="n">
+        <v>359</v>
+      </c>
+      <c r="P146" s="22" t="n">
+        <v>1297</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>-2845</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>6140</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>-5699</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-3639</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>27100</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>-26066</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Short Term Investments Inv CF</t>
+          <t>선수금 증감</t>
         </is>
       </c>
       <c r="C147" s="22" t="n">
-        <v>-10000</v>
+        <v>18898</v>
+      </c>
+      <c r="E147" s="22" t="n">
+        <v>-2390</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>-10000</v>
+        <v>8761</v>
+      </c>
+      <c r="I147" s="22" t="n">
+        <v>-32512</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>0</v>
+        <v>-33752</v>
+      </c>
+      <c r="M147" s="22" t="n">
+        <v>11426</v>
+      </c>
+      <c r="O147" s="22" t="n">
+        <v>34444</v>
+      </c>
+      <c r="P147" s="22" t="n">
+        <v>31684</v>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>-22077</v>
+      </c>
+      <c r="R147" s="22" t="n">
+        <v>58630</v>
+      </c>
+      <c r="S147" s="22" t="n">
+        <v>-54851</v>
+      </c>
+      <c r="T147" s="22" t="n">
+        <v>32031</v>
+      </c>
+      <c r="U147" s="22" t="n">
+        <v>185616</v>
+      </c>
+      <c r="V147" s="22" t="n">
+        <v>-2390</v>
+      </c>
+      <c r="W147" s="22" t="n">
+        <v>-32512</v>
+      </c>
+      <c r="X147" s="22" t="n">
+        <v>11426</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="n">
+        <v>-12397</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-755</v>
+        <v>-10671</v>
+      </c>
+      <c r="G148" s="22" t="n">
+        <v>-1706</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>-767</v>
+        <v>10365</v>
+      </c>
+      <c r="K148" s="22" t="n">
+        <v>-3915</v>
       </c>
       <c r="M148" s="22" t="n">
+        <v>11105</v>
+      </c>
+      <c r="O148" s="22" t="n">
+        <v>5843</v>
+      </c>
+      <c r="P148" s="22" t="n">
+        <v>24136</v>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>1399</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>4387</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>4766</v>
+      </c>
+      <c r="T148" s="22" t="n">
+        <v>7070</v>
+      </c>
+      <c r="U148" s="22" t="n">
         <v>-809</v>
       </c>
-      <c r="O148" s="22" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="P148" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" s="22" t="n">
-        <v>-10449</v>
-      </c>
-      <c r="S148" s="22" t="n">
-        <v>-568</v>
-      </c>
-      <c r="T148" s="22" t="n">
-        <v>-641</v>
-      </c>
-      <c r="U148" s="22" t="n">
-        <v>-713</v>
-      </c>
       <c r="V148" s="22" t="n">
-        <v>-755</v>
+        <v>-10671</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>-767</v>
+        <v>10365</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>-809</v>
+        <v>11105</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="n">
+        <v>269814</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>665</v>
+        <v>549109</v>
+      </c>
+      <c r="G149" s="22" t="n">
+        <v>409148</v>
       </c>
       <c r="I149" s="22" t="n">
-        <v>756</v>
+        <v>720516</v>
+      </c>
+      <c r="K149" s="22" t="n">
+        <v>356490</v>
       </c>
       <c r="M149" s="22" t="n">
-        <v>800</v>
+        <v>714029</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>50034</v>
+        <v>168304</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>0</v>
+        <v>235238</v>
+      </c>
+      <c r="Q149" s="22" t="n">
+        <v>289766</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>0</v>
+        <v>292679</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>10506</v>
+        <v>231990</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>604</v>
+        <v>387252</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>731</v>
+        <v>632473</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>665</v>
+        <v>549109</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>756</v>
+        <v>720516</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>800</v>
+        <v>714029</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>Payment For Purchase Of Short Term Investments Inv CF</t>
-        </is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="n">
+        <v>2779</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-20000</v>
+        <v>4546</v>
+      </c>
+      <c r="G150" s="22" t="n">
+        <v>3359</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-30000</v>
+        <v>4472</v>
+      </c>
+      <c r="K150" s="22" t="n">
+        <v>2788</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-10000</v>
+        <v>4075</v>
       </c>
       <c r="O150" s="22" t="n">
-        <v>-177200</v>
+        <v>1266</v>
       </c>
       <c r="P150" s="22" t="n">
-        <v>-131000</v>
+        <v>1115</v>
       </c>
       <c r="Q150" s="22" t="n">
-        <v>-209500</v>
+        <v>2738</v>
       </c>
       <c r="R150" s="22" t="n">
-        <v>-90000</v>
+        <v>2326</v>
       </c>
       <c r="S150" s="22" t="n">
-        <v>-45000</v>
+        <v>1669</v>
       </c>
       <c r="T150" s="22" t="n">
-        <v>-35000</v>
+        <v>2232</v>
       </c>
       <c r="U150" s="22" t="n">
-        <v>0</v>
+        <v>2907</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-20000</v>
+        <v>4546</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-30000</v>
+        <v>4472</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-10000</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Redemption Of Short Term Investments Inv CF</t>
-        </is>
+          <t>법인세 납부·환급</t>
+        </is>
+      </c>
+      <c r="C151" s="22" t="n">
+        <v>-71971</v>
       </c>
       <c r="E151" s="22" t="n">
-        <v>10001</v>
+        <v>-118935</v>
+      </c>
+      <c r="G151" s="22" t="n">
+        <v>-80074</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>30167</v>
+        <v>-142814</v>
+      </c>
+      <c r="K151" s="22" t="n">
+        <v>-108429</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>20000</v>
+        <v>-178372</v>
       </c>
       <c r="O151" s="22" t="n">
-        <v>142198</v>
+        <v>-32622</v>
       </c>
       <c r="P151" s="22" t="n">
-        <v>166000</v>
+        <v>-49771</v>
       </c>
       <c r="Q151" s="22" t="n">
-        <v>165500</v>
+        <v>-102932</v>
       </c>
       <c r="R151" s="22" t="n">
-        <v>170000</v>
+        <v>-41888</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>80000</v>
+        <v>-87772</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>45014</v>
+        <v>-106098</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>35000</v>
+        <v>-209111</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>10001</v>
+        <v>-118935</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>30167</v>
+        <v>-142814</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>20000</v>
+        <v>-178372</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="20" t="inlineStr">
-        <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="C152" s="22" t="n">
-        <v>-54953</v>
-      </c>
-      <c r="E152" s="22" t="n">
-        <v>-116993</v>
-      </c>
-      <c r="G152" s="22" t="n">
-        <v>-77961</v>
-      </c>
-      <c r="I152" s="22" t="n">
-        <v>-158374</v>
-      </c>
-      <c r="K152" s="22" t="n">
-        <v>-135392</v>
-      </c>
-      <c r="M152" s="22" t="n">
-        <v>-208984</v>
-      </c>
-      <c r="O152" s="22" t="n">
-        <v>-17557</v>
-      </c>
-      <c r="P152" s="22" t="n">
-        <v>-41750</v>
-      </c>
-      <c r="Q152" s="22" t="n">
-        <v>-46517</v>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>-49369</v>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>-53806</v>
-      </c>
-      <c r="T152" s="22" t="n">
-        <v>-56153</v>
-      </c>
-      <c r="U152" s="22" t="n">
-        <v>-66897</v>
-      </c>
-      <c r="V152" s="22" t="n">
-        <v>-116993</v>
-      </c>
-      <c r="W152" s="22" t="n">
-        <v>-158374</v>
-      </c>
-      <c r="X152" s="22" t="n">
-        <v>-208984</v>
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="n">
+        <v>200622</v>
+      </c>
+      <c r="E152" s="12" t="n">
+        <v>434720</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>332433</v>
+      </c>
+      <c r="I152" s="12" t="n">
+        <v>582174</v>
+      </c>
+      <c r="K152" s="12" t="n">
+        <v>250848</v>
+      </c>
+      <c r="M152" s="12" t="n">
+        <v>539732</v>
+      </c>
+      <c r="O152" s="12" t="n">
+        <v>136948</v>
+      </c>
+      <c r="P152" s="12" t="n">
+        <v>186582</v>
+      </c>
+      <c r="Q152" s="12" t="n">
+        <v>189572</v>
+      </c>
+      <c r="R152" s="12" t="n">
+        <v>253117</v>
+      </c>
+      <c r="S152" s="12" t="n">
+        <v>145888</v>
+      </c>
+      <c r="T152" s="12" t="n">
+        <v>283387</v>
+      </c>
+      <c r="U152" s="12" t="n">
+        <v>426270</v>
+      </c>
+      <c r="V152" s="12" t="n">
+        <v>434720</v>
+      </c>
+      <c r="W152" s="12" t="n">
+        <v>582174</v>
+      </c>
+      <c r="X152" s="12" t="n">
+        <v>539732</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
-      </c>
-      <c r="E153" s="22" t="n">
-        <v>12967</v>
-      </c>
-      <c r="U153" s="22" t="n">
-        <v>1428</v>
-      </c>
-      <c r="V153" s="22" t="n">
-        <v>12967</v>
+          <t>정기예금 증감</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="n">
+        <v>-83</v>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>Decrease Increase In Short Term Investments Inv CF</t>
         </is>
       </c>
       <c r="C154" s="22" t="n">
-        <v>-3833</v>
-      </c>
-      <c r="E154" s="22" t="n">
-        <v>-7987</v>
+        <v>-10000</v>
       </c>
       <c r="G154" s="22" t="n">
-        <v>-3435</v>
-      </c>
-      <c r="I154" s="22" t="n">
-        <v>-9665</v>
+        <v>-10000</v>
       </c>
       <c r="K154" s="22" t="n">
-        <v>-4533</v>
-      </c>
-      <c r="M154" s="22" t="n">
-        <v>-10457</v>
-      </c>
-      <c r="O154" s="22" t="n">
-        <v>-1116</v>
-      </c>
-      <c r="P154" s="22" t="n">
-        <v>-4431</v>
-      </c>
-      <c r="Q154" s="22" t="n">
-        <v>-1563</v>
-      </c>
-      <c r="R154" s="22" t="n">
-        <v>-3383</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>-7124</v>
-      </c>
-      <c r="T154" s="22" t="n">
-        <v>-8950</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>-9416</v>
-      </c>
-      <c r="V154" s="22" t="n">
-        <v>-7987</v>
-      </c>
-      <c r="W154" s="22" t="n">
-        <v>-9665</v>
-      </c>
-      <c r="X154" s="22" t="n">
-        <v>-10457</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 매각</t>
-        </is>
+          <t>정기예금 예입</t>
+        </is>
+      </c>
+      <c r="E155" s="22" t="n">
+        <v>-755</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>-767</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>-809</v>
+      </c>
+      <c r="O155" s="22" t="n">
+        <v>-25000</v>
       </c>
       <c r="P155" s="22" t="n">
         <v>0</v>
       </c>
       <c r="Q155" s="22" t="n">
-        <v>10754</v>
+        <v>0</v>
       </c>
       <c r="R155" s="22" t="n">
-        <v>0</v>
+        <v>-10449</v>
+      </c>
+      <c r="S155" s="22" t="n">
+        <v>-568</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>-641</v>
+      </c>
+      <c r="U155" s="22" t="n">
+        <v>-713</v>
+      </c>
+      <c r="V155" s="22" t="n">
+        <v>-755</v>
+      </c>
+      <c r="W155" s="22" t="n">
+        <v>-767</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>-809</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
-        </is>
+          <t>정기예금 인출</t>
+        </is>
+      </c>
+      <c r="E156" s="22" t="n">
+        <v>665</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>1712</v>
+        <v>756</v>
       </c>
       <c r="M156" s="22" t="n">
-        <v>117387</v>
+        <v>800</v>
+      </c>
+      <c r="O156" s="22" t="n">
+        <v>50034</v>
+      </c>
+      <c r="P156" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" s="22" t="n">
+        <v>10506</v>
+      </c>
+      <c r="T156" s="22" t="n">
+        <v>604</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>731</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>665</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>1712</v>
+        <v>756</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>117387</v>
+        <v>800</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C157" s="22" t="n">
-        <v>-1483</v>
+          <t>Payment For Purchase Of Short Term Investments Inv CF</t>
+        </is>
       </c>
       <c r="E157" s="22" t="n">
-        <v>9921</v>
-      </c>
-      <c r="G157" s="22" t="n">
-        <v>-397</v>
+        <v>-20000</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>-3438</v>
-      </c>
-      <c r="K157" s="22" t="n">
-        <v>-1044</v>
+        <v>-30000</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>-4429</v>
+        <v>-10000</v>
       </c>
       <c r="O157" s="22" t="n">
-        <v>-252</v>
+        <v>-177200</v>
       </c>
       <c r="P157" s="22" t="n">
-        <v>-5082</v>
+        <v>-131000</v>
       </c>
       <c r="Q157" s="22" t="n">
-        <v>-2707</v>
+        <v>-209500</v>
       </c>
       <c r="R157" s="22" t="n">
-        <v>-845</v>
+        <v>-90000</v>
       </c>
       <c r="S157" s="22" t="n">
-        <v>7656</v>
+        <v>-45000</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>-504</v>
+        <v>-35000</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>-1887</v>
+        <v>0</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>9921</v>
+        <v>-20000</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>-3438</v>
+        <v>-30000</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>-4429</v>
+        <v>-10000</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C158" s="12" t="n">
-        <v>-70354</v>
-      </c>
-      <c r="E158" s="12" t="n">
-        <v>-125148</v>
-      </c>
-      <c r="G158" s="12" t="n">
-        <v>-91799</v>
-      </c>
-      <c r="I158" s="12" t="n">
-        <v>-169609</v>
-      </c>
-      <c r="K158" s="12" t="n">
-        <v>-140971</v>
-      </c>
-      <c r="M158" s="12" t="n">
-        <v>-96492</v>
-      </c>
-      <c r="O158" s="12" t="n">
-        <v>-28893</v>
-      </c>
-      <c r="P158" s="12" t="n">
-        <v>-11833</v>
-      </c>
-      <c r="Q158" s="12" t="n">
-        <v>-84033</v>
-      </c>
-      <c r="R158" s="12" t="n">
-        <v>15951</v>
-      </c>
-      <c r="S158" s="12" t="n">
-        <v>-18274</v>
-      </c>
-      <c r="T158" s="12" t="n">
-        <v>-55632</v>
-      </c>
-      <c r="U158" s="12" t="n">
-        <v>-41756</v>
-      </c>
-      <c r="V158" s="12" t="n">
-        <v>-125148</v>
-      </c>
-      <c r="W158" s="12" t="n">
-        <v>-169609</v>
-      </c>
-      <c r="X158" s="12" t="n">
-        <v>-96492</v>
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>Proceeds From Redemption Of Short Term Investments Inv CF</t>
+        </is>
+      </c>
+      <c r="E158" s="22" t="n">
+        <v>10001</v>
+      </c>
+      <c r="I158" s="22" t="n">
+        <v>30167</v>
+      </c>
+      <c r="M158" s="22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="O158" s="22" t="n">
+        <v>142198</v>
+      </c>
+      <c r="P158" s="22" t="n">
+        <v>166000</v>
+      </c>
+      <c r="Q158" s="22" t="n">
+        <v>165500</v>
+      </c>
+      <c r="R158" s="22" t="n">
+        <v>170000</v>
+      </c>
+      <c r="S158" s="22" t="n">
+        <v>80000</v>
+      </c>
+      <c r="T158" s="22" t="n">
+        <v>45014</v>
+      </c>
+      <c r="U158" s="22" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V158" s="22" t="n">
+        <v>10001</v>
+      </c>
+      <c r="W158" s="22" t="n">
+        <v>30167</v>
+      </c>
+      <c r="X158" s="22" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C159" s="22" t="n">
-        <v>-120027</v>
+        <v>-54953</v>
       </c>
       <c r="E159" s="22" t="n">
-        <v>-120028</v>
+        <v>-116993</v>
       </c>
       <c r="G159" s="22" t="n">
-        <v>-80002</v>
+        <v>-77961</v>
       </c>
       <c r="I159" s="22" t="n">
-        <v>-150008</v>
+        <v>-158374</v>
       </c>
       <c r="K159" s="22" t="n">
-        <v>-1</v>
+        <v>-135392</v>
       </c>
       <c r="M159" s="22" t="n">
-        <v>-150010</v>
+        <v>-208984</v>
       </c>
       <c r="O159" s="22" t="n">
-        <v>-6</v>
+        <v>-17557</v>
       </c>
       <c r="P159" s="22" t="n">
-        <v>-16</v>
+        <v>-41750</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>-5004</v>
+        <v>-46517</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>-154096</v>
+        <v>-49369</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>-4339</v>
+        <v>-53806</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>-15</v>
+        <v>-56153</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>-1728</v>
+        <v>-66897</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>-120028</v>
+        <v>-116993</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-150008</v>
+        <v>-158374</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>-150010</v>
+        <v>-208984</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="C160" s="22" t="n">
-        <v>-133754</v>
+          <t>유형자산 매각</t>
+        </is>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-202457</v>
-      </c>
-      <c r="G160" s="22" t="n">
-        <v>-113767</v>
-      </c>
-      <c r="I160" s="22" t="n">
-        <v>-236276</v>
-      </c>
-      <c r="K160" s="22" t="n">
-        <v>-150254</v>
-      </c>
-      <c r="M160" s="22" t="n">
-        <v>-271618</v>
-      </c>
-      <c r="O160" s="22" t="n">
-        <v>-39371</v>
-      </c>
-      <c r="P160" s="22" t="n">
-        <v>-82203</v>
-      </c>
-      <c r="Q160" s="22" t="n">
-        <v>-124754</v>
-      </c>
-      <c r="R160" s="22" t="n">
-        <v>-95513</v>
-      </c>
-      <c r="S160" s="22" t="n">
-        <v>-109542</v>
-      </c>
-      <c r="T160" s="22" t="n">
-        <v>-166252</v>
+        <v>12967</v>
       </c>
       <c r="U160" s="22" t="n">
-        <v>-252988</v>
+        <v>1428</v>
       </c>
       <c r="V160" s="22" t="n">
-        <v>-202457</v>
-      </c>
-      <c r="W160" s="22" t="n">
-        <v>-236276</v>
-      </c>
-      <c r="X160" s="22" t="n">
-        <v>-271618</v>
+        <v>12967</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>무형자산 취득</t>
         </is>
       </c>
       <c r="C161" s="22" t="n">
-        <v>-1217</v>
+        <v>-3833</v>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-2525</v>
+        <v>-7987</v>
       </c>
       <c r="G161" s="22" t="n">
-        <v>-1322</v>
+        <v>-3435</v>
       </c>
       <c r="I161" s="22" t="n">
-        <v>-2551</v>
+        <v>-9665</v>
       </c>
       <c r="K161" s="22" t="n">
-        <v>-1887</v>
+        <v>-4533</v>
       </c>
       <c r="M161" s="22" t="n">
-        <v>-3730</v>
+        <v>-10457</v>
       </c>
       <c r="O161" s="22" t="n">
-        <v>-2</v>
+        <v>-1116</v>
       </c>
       <c r="P161" s="22" t="n">
-        <v>-329</v>
+        <v>-4431</v>
       </c>
       <c r="Q161" s="22" t="n">
-        <v>-3</v>
+        <v>-1563</v>
       </c>
       <c r="R161" s="22" t="n">
-        <v>-764</v>
+        <v>-3383</v>
       </c>
       <c r="S161" s="22" t="n">
-        <v>-643</v>
+        <v>-7124</v>
       </c>
       <c r="T161" s="22" t="n">
-        <v>-988</v>
+        <v>-8950</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>-1817</v>
+        <v>-9416</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-2525</v>
+        <v>-7987</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>-2551</v>
+        <v>-9665</v>
       </c>
       <c r="X161" s="22" t="n">
-        <v>-3730</v>
+        <v>-10457</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C162" s="12" t="n">
-        <v>-254999</v>
-      </c>
-      <c r="E162" s="12" t="n">
-        <v>-325012</v>
-      </c>
-      <c r="G162" s="12" t="n">
-        <v>-195092</v>
-      </c>
-      <c r="I162" s="12" t="n">
-        <v>-388836</v>
-      </c>
-      <c r="K162" s="12" t="n">
-        <v>-152143</v>
-      </c>
-      <c r="M162" s="12" t="n">
-        <v>-425359</v>
-      </c>
-      <c r="O162" s="12" t="n">
-        <v>-39380</v>
-      </c>
-      <c r="P162" s="12" t="n">
-        <v>-82549</v>
-      </c>
-      <c r="Q162" s="12" t="n">
-        <v>-129761</v>
-      </c>
-      <c r="R162" s="12" t="n">
-        <v>-250374</v>
-      </c>
-      <c r="S162" s="12" t="n">
-        <v>-114525</v>
-      </c>
-      <c r="T162" s="12" t="n">
-        <v>-167256</v>
-      </c>
-      <c r="U162" s="12" t="n">
-        <v>-256534</v>
-      </c>
-      <c r="V162" s="12" t="n">
-        <v>-325012</v>
-      </c>
-      <c r="W162" s="12" t="n">
-        <v>-388836</v>
-      </c>
-      <c r="X162" s="12" t="n">
-        <v>-425359</v>
+      <c r="A162" s="20" t="inlineStr">
+        <is>
+          <t>연결범위 변경 자회사 주식 매각</t>
+        </is>
+      </c>
+      <c r="P162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="22" t="n">
+        <v>10754</v>
+      </c>
+      <c r="R162" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="C163" s="22" t="n">
-        <v>4153</v>
-      </c>
-      <c r="E163" s="22" t="n">
-        <v>4577</v>
-      </c>
-      <c r="G163" s="22" t="n">
-        <v>-2481</v>
+          <t>투자유가증권 매각</t>
+        </is>
       </c>
       <c r="I163" s="22" t="n">
-        <v>-264</v>
-      </c>
-      <c r="K163" s="22" t="n">
-        <v>1206</v>
+        <v>1712</v>
       </c>
       <c r="M163" s="22" t="n">
-        <v>2461</v>
-      </c>
-      <c r="O163" s="22" t="n">
-        <v>53</v>
-      </c>
-      <c r="P163" s="22" t="n">
-        <v>1312</v>
-      </c>
-      <c r="Q163" s="22" t="n">
-        <v>-1020</v>
-      </c>
-      <c r="R163" s="22" t="n">
-        <v>-3369</v>
-      </c>
-      <c r="S163" s="22" t="n">
-        <v>4946</v>
-      </c>
-      <c r="T163" s="22" t="n">
-        <v>9156</v>
-      </c>
-      <c r="U163" s="22" t="n">
-        <v>8843</v>
-      </c>
-      <c r="V163" s="22" t="n">
-        <v>4577</v>
+        <v>117387</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>-264</v>
+        <v>1712</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>2461</v>
+        <v>117387</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="n">
+        <v>-1483</v>
+      </c>
+      <c r="E164" s="22" t="n">
+        <v>9921</v>
+      </c>
+      <c r="G164" s="22" t="n">
+        <v>-397</v>
+      </c>
+      <c r="I164" s="22" t="n">
+        <v>-3438</v>
+      </c>
+      <c r="K164" s="22" t="n">
+        <v>-1044</v>
+      </c>
+      <c r="M164" s="22" t="n">
+        <v>-4429</v>
+      </c>
+      <c r="O164" s="22" t="n">
+        <v>-252</v>
+      </c>
+      <c r="P164" s="22" t="n">
+        <v>-5082</v>
+      </c>
+      <c r="Q164" s="22" t="n">
+        <v>-2707</v>
+      </c>
+      <c r="R164" s="22" t="n">
+        <v>-845</v>
+      </c>
+      <c r="S164" s="22" t="n">
+        <v>7656</v>
+      </c>
+      <c r="T164" s="22" t="n">
+        <v>-504</v>
+      </c>
+      <c r="U164" s="22" t="n">
+        <v>-1887</v>
+      </c>
+      <c r="V164" s="22" t="n">
+        <v>9921</v>
+      </c>
+      <c r="W164" s="22" t="n">
+        <v>-3438</v>
+      </c>
+      <c r="X164" s="22" t="n">
+        <v>-4429</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="n">
+        <v>-70354</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>-125148</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>-91799</v>
+      </c>
+      <c r="I165" s="12" t="n">
+        <v>-169609</v>
+      </c>
+      <c r="K165" s="12" t="n">
+        <v>-140971</v>
+      </c>
+      <c r="M165" s="12" t="n">
+        <v>-96492</v>
+      </c>
+      <c r="O165" s="12" t="n">
+        <v>-28893</v>
+      </c>
+      <c r="P165" s="12" t="n">
+        <v>-11833</v>
+      </c>
+      <c r="Q165" s="12" t="n">
+        <v>-84033</v>
+      </c>
+      <c r="R165" s="12" t="n">
+        <v>15951</v>
+      </c>
+      <c r="S165" s="12" t="n">
+        <v>-18274</v>
+      </c>
+      <c r="T165" s="12" t="n">
+        <v>-55632</v>
+      </c>
+      <c r="U165" s="12" t="n">
+        <v>-41756</v>
+      </c>
+      <c r="V165" s="12" t="n">
+        <v>-125148</v>
+      </c>
+      <c r="W165" s="12" t="n">
+        <v>-169609</v>
+      </c>
+      <c r="X165" s="12" t="n">
+        <v>-96492</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="n">
+        <v>-120027</v>
+      </c>
+      <c r="E166" s="22" t="n">
+        <v>-120028</v>
+      </c>
+      <c r="G166" s="22" t="n">
+        <v>-80002</v>
+      </c>
+      <c r="I166" s="22" t="n">
+        <v>-150008</v>
+      </c>
+      <c r="K166" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M166" s="22" t="n">
+        <v>-150010</v>
+      </c>
+      <c r="O166" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P166" s="22" t="n">
+        <v>-16</v>
+      </c>
+      <c r="Q166" s="22" t="n">
+        <v>-5004</v>
+      </c>
+      <c r="R166" s="22" t="n">
+        <v>-154096</v>
+      </c>
+      <c r="S166" s="22" t="n">
+        <v>-4339</v>
+      </c>
+      <c r="T166" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="U166" s="22" t="n">
+        <v>-1728</v>
+      </c>
+      <c r="V166" s="22" t="n">
+        <v>-120028</v>
+      </c>
+      <c r="W166" s="22" t="n">
+        <v>-150008</v>
+      </c>
+      <c r="X166" s="22" t="n">
+        <v>-150010</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="C167" s="22" t="n">
+        <v>-133754</v>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>-202457</v>
+      </c>
+      <c r="G167" s="22" t="n">
+        <v>-113767</v>
+      </c>
+      <c r="I167" s="22" t="n">
+        <v>-236276</v>
+      </c>
+      <c r="K167" s="22" t="n">
+        <v>-150254</v>
+      </c>
+      <c r="M167" s="22" t="n">
+        <v>-271618</v>
+      </c>
+      <c r="O167" s="22" t="n">
+        <v>-39371</v>
+      </c>
+      <c r="P167" s="22" t="n">
+        <v>-82203</v>
+      </c>
+      <c r="Q167" s="22" t="n">
+        <v>-124754</v>
+      </c>
+      <c r="R167" s="22" t="n">
+        <v>-95513</v>
+      </c>
+      <c r="S167" s="22" t="n">
+        <v>-109542</v>
+      </c>
+      <c r="T167" s="22" t="n">
+        <v>-166252</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>-252988</v>
+      </c>
+      <c r="V167" s="22" t="n">
+        <v>-202457</v>
+      </c>
+      <c r="W167" s="22" t="n">
+        <v>-236276</v>
+      </c>
+      <c r="X167" s="22" t="n">
+        <v>-271618</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="n">
+        <v>-1217</v>
+      </c>
+      <c r="E168" s="22" t="n">
+        <v>-2525</v>
+      </c>
+      <c r="G168" s="22" t="n">
+        <v>-1322</v>
+      </c>
+      <c r="I168" s="22" t="n">
+        <v>-2551</v>
+      </c>
+      <c r="K168" s="22" t="n">
+        <v>-1887</v>
+      </c>
+      <c r="M168" s="22" t="n">
+        <v>-3730</v>
+      </c>
+      <c r="O168" s="22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P168" s="22" t="n">
+        <v>-329</v>
+      </c>
+      <c r="Q168" s="22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R168" s="22" t="n">
+        <v>-764</v>
+      </c>
+      <c r="S168" s="22" t="n">
+        <v>-643</v>
+      </c>
+      <c r="T168" s="22" t="n">
+        <v>-988</v>
+      </c>
+      <c r="U168" s="22" t="n">
+        <v>-1817</v>
+      </c>
+      <c r="V168" s="22" t="n">
+        <v>-2525</v>
+      </c>
+      <c r="W168" s="22" t="n">
+        <v>-2551</v>
+      </c>
+      <c r="X168" s="22" t="n">
+        <v>-3730</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="n">
+        <v>-254999</v>
+      </c>
+      <c r="E169" s="12" t="n">
+        <v>-325012</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>-195092</v>
+      </c>
+      <c r="I169" s="12" t="n">
+        <v>-388836</v>
+      </c>
+      <c r="K169" s="12" t="n">
+        <v>-152143</v>
+      </c>
+      <c r="M169" s="12" t="n">
+        <v>-425359</v>
+      </c>
+      <c r="O169" s="12" t="n">
+        <v>-39380</v>
+      </c>
+      <c r="P169" s="12" t="n">
+        <v>-82549</v>
+      </c>
+      <c r="Q169" s="12" t="n">
+        <v>-129761</v>
+      </c>
+      <c r="R169" s="12" t="n">
+        <v>-250374</v>
+      </c>
+      <c r="S169" s="12" t="n">
+        <v>-114525</v>
+      </c>
+      <c r="T169" s="12" t="n">
+        <v>-167256</v>
+      </c>
+      <c r="U169" s="12" t="n">
+        <v>-256534</v>
+      </c>
+      <c r="V169" s="12" t="n">
+        <v>-325012</v>
+      </c>
+      <c r="W169" s="12" t="n">
+        <v>-388836</v>
+      </c>
+      <c r="X169" s="12" t="n">
+        <v>-425359</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E170" s="22" t="n">
+        <v>4577</v>
+      </c>
+      <c r="G170" s="22" t="n">
+        <v>-2481</v>
+      </c>
+      <c r="I170" s="22" t="n">
+        <v>-264</v>
+      </c>
+      <c r="K170" s="22" t="n">
+        <v>1206</v>
+      </c>
+      <c r="M170" s="22" t="n">
+        <v>2461</v>
+      </c>
+      <c r="O170" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="P170" s="22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="Q170" s="22" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="R170" s="22" t="n">
+        <v>-3369</v>
+      </c>
+      <c r="S170" s="22" t="n">
+        <v>4946</v>
+      </c>
+      <c r="T170" s="22" t="n">
+        <v>9156</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>8843</v>
+      </c>
+      <c r="V170" s="22" t="n">
+        <v>4577</v>
+      </c>
+      <c r="W170" s="22" t="n">
+        <v>-264</v>
+      </c>
+      <c r="X170" s="22" t="n">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C164" s="22" t="n">
+      <c r="C171" s="22" t="n">
         <v>-120578</v>
       </c>
-      <c r="E164" s="22" t="n">
+      <c r="E171" s="22" t="n">
         <v>-10862</v>
       </c>
-      <c r="G164" s="22" t="n">
+      <c r="G171" s="22" t="n">
         <v>43060</v>
       </c>
-      <c r="I164" s="22" t="n">
+      <c r="I171" s="22" t="n">
         <v>23463</v>
       </c>
-      <c r="K164" s="22" t="n">
+      <c r="K171" s="22" t="n">
         <v>-41058</v>
       </c>
-      <c r="M164" s="22" t="n">
+      <c r="M171" s="22" t="n">
         <v>20342</v>
       </c>
-      <c r="O164" s="22" t="n">
+      <c r="O171" s="22" t="n">
         <v>68728</v>
       </c>
-      <c r="P164" s="22" t="n">
+      <c r="P171" s="22" t="n">
         <v>93511</v>
       </c>
-      <c r="Q164" s="22" t="n">
+      <c r="Q171" s="22" t="n">
         <v>-25243</v>
       </c>
-      <c r="R164" s="22" t="n">
+      <c r="R171" s="22" t="n">
         <v>15324</v>
       </c>
-      <c r="S164" s="22" t="n">
+      <c r="S171" s="22" t="n">
         <v>18033</v>
       </c>
-      <c r="T164" s="22" t="n">
+      <c r="T171" s="22" t="n">
         <v>69655</v>
       </c>
-      <c r="U164" s="22" t="n">
+      <c r="U171" s="22" t="n">
         <v>136823</v>
       </c>
-      <c r="V164" s="22" t="n">
+      <c r="V171" s="22" t="n">
         <v>-10862</v>
       </c>
-      <c r="W164" s="22" t="n">
+      <c r="W171" s="22" t="n">
         <v>23463</v>
       </c>
-      <c r="X164" s="22" t="n">
+      <c r="X171" s="22" t="n">
         <v>20342</v>
       </c>
     </row>
@@ -9934,7 +10405,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11342,7 +11813,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11394,7 +11865,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11446,7 +11917,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11498,7 +11969,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11550,7 +12021,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11602,7 +12073,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11654,7 +12125,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11664,43 +12135,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11724,7 +12195,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11776,7 +12247,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11828,7 +12299,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11880,7 +12351,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11932,7 +12403,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11984,7 +12455,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12054,7 +12525,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12106,7 +12577,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12116,49 +12587,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12168,49 +12639,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12220,49 +12691,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12272,43 +12743,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12332,7 +12803,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12384,7 +12855,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12436,7 +12907,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12488,7 +12959,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14692,24 +15163,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/8035.xlsx
+++ b/docs/data/jp/xlsx/8035.xlsx
@@ -8656,7 +8656,7 @@
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>Gain On Refund Of Value Added Tax EI</t>
+          <t>부가가치세 환급금</t>
         </is>
       </c>
       <c r="E110" s="22" t="n">
@@ -8939,7 +8939,7 @@
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>Provision For Loss On Litigation EL</t>
+          <t>소송 손실 충당금 전입액</t>
         </is>
       </c>
       <c r="H117" s="22" t="n">
@@ -11516,7 +11516,7 @@
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>Payment For Purchase Of Short Term Investments Inv CF</t>
+          <t>단기투자 취득 지출</t>
         </is>
       </c>
       <c r="D168" s="22" t="n">
@@ -11562,7 +11562,7 @@
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Redemption Of Short Term Investments Inv CF</t>
+          <t>단기투자 상환 수입</t>
         </is>
       </c>
       <c r="D169" s="22" t="n">
@@ -11624,7 +11624,7 @@
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Short Term Investments Inv CF</t>
+          <t>단기투자 증감액(△는 증가)</t>
         </is>
       </c>
       <c r="F171" s="22" t="n">
